--- a/ゾンビシューターゲームコスト表.xlsx
+++ b/ゾンビシューターゲームコスト表.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\由留部 瑛人\Documents\MyGame3D2\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sho24\OneDrive\ドキュメント\MyGame3D2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F5017835-09C6-4AA5-8134-3E57B7E9655B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{975B0F2C-61C8-4863-AC78-ECC6AF9AD5B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1350" yWindow="1830" windowWidth="23610" windowHeight="13035" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4170" yWindow="1155" windowWidth="21600" windowHeight="11295" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="コスト表" sheetId="1" r:id="rId1"/>
@@ -18,7 +18,7 @@
     <sheet name="その他" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">コスト表!$E$2:$G$133</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">コスト表!$E$2:$G$132</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">分類別コスト集計!$B$2:$G$21</definedName>
   </definedNames>
   <calcPr calcId="191028"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="562" uniqueCount="159">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="557" uniqueCount="159">
   <si>
     <t>分類</t>
   </si>
@@ -1964,7 +1964,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B1:I133"/>
+  <dimension ref="B1:I132"/>
   <sheetFormatPr defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col min="2" max="2" width="27.5" bestFit="1" customWidth="1"/>
@@ -3652,7 +3652,7 @@
         <v>9</v>
       </c>
       <c r="G84" s="11" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H84" s="15"/>
     </row>
@@ -3682,7 +3682,7 @@
         <v>17</v>
       </c>
       <c r="G86" s="11" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="H86" s="15"/>
     </row>
@@ -3766,7 +3766,7 @@
         <v>9</v>
       </c>
       <c r="G90" s="11" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H90" s="15"/>
     </row>
@@ -3796,7 +3796,7 @@
         <v>9</v>
       </c>
       <c r="G92" s="10" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H92" s="14"/>
     </row>
@@ -4053,7 +4053,7 @@
         <v>9</v>
       </c>
       <c r="G105" s="10" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H105" s="15"/>
     </row>
@@ -4123,34 +4123,18 @@
       </c>
     </row>
     <row r="109" spans="2:8" ht="18.75">
-      <c r="B109" s="1" t="s">
-        <v>142</v>
-      </c>
-      <c r="C109" s="1" t="s">
-        <v>109</v>
-      </c>
-      <c r="D109" s="7">
-        <v>0.5</v>
-      </c>
-      <c r="E109" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="F109" s="11" t="s">
-        <v>9</v>
-      </c>
-      <c r="G109" s="11" t="s">
-        <v>10</v>
-      </c>
-      <c r="H109" s="15"/>
+      <c r="B109" s="2"/>
+      <c r="C109" s="2"/>
+      <c r="D109" s="9"/>
+      <c r="E109" s="6"/>
+      <c r="F109" s="12"/>
+      <c r="G109" s="12"/>
+      <c r="H109" s="16"/>
     </row>
     <row r="110" spans="2:8" ht="18.75">
-      <c r="B110" s="2"/>
-      <c r="C110" s="2"/>
-      <c r="D110" s="9"/>
-      <c r="E110" s="6"/>
-      <c r="F110" s="12"/>
-      <c r="G110" s="12"/>
-      <c r="H110" s="16"/>
+      <c r="C110"/>
+      <c r="D110" s="7"/>
+      <c r="H110" s="13"/>
     </row>
     <row r="111" spans="2:8" ht="18.75">
       <c r="C111"/>
@@ -4207,26 +4191,26 @@
       <c r="D121" s="7"/>
       <c r="H121" s="13"/>
     </row>
-    <row r="122" spans="3:8" ht="18.75">
-      <c r="C122"/>
-      <c r="D122" s="7"/>
-      <c r="H122" s="13"/>
-    </row>
+    <row r="122" spans="3:8" ht="18.75"/>
     <row r="123" spans="3:8" ht="18.75"/>
     <row r="124" spans="3:8" ht="18.75"/>
     <row r="125" spans="3:8" ht="18.75"/>
-    <row r="126" spans="3:8" ht="18.75"/>
+    <row r="126" spans="3:8" ht="18.75">
+      <c r="C126"/>
+      <c r="D126" s="7"/>
+      <c r="H126" s="13"/>
+    </row>
     <row r="127" spans="3:8" ht="18.75">
       <c r="C127"/>
       <c r="D127" s="7"/>
       <c r="H127" s="13"/>
     </row>
     <row r="128" spans="3:8" ht="18.75">
-      <c r="C128"/>
-      <c r="D128" s="7"/>
       <c r="H128" s="13"/>
     </row>
     <row r="129" spans="3:8" ht="18.75">
+      <c r="C129"/>
+      <c r="D129" s="7"/>
       <c r="H129" s="13"/>
     </row>
     <row r="130" spans="3:8" ht="18.75">
@@ -4244,13 +4228,8 @@
       <c r="D132" s="7"/>
       <c r="H132" s="13"/>
     </row>
-    <row r="133" spans="3:8" ht="18.75">
-      <c r="C133"/>
-      <c r="D133" s="7"/>
-      <c r="H133" s="13"/>
-    </row>
   </sheetData>
-  <autoFilter ref="E2:G133" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter ref="E2:G132" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="1200" verticalDpi="1200"/>
@@ -4261,19 +4240,19 @@
           <x14:formula1>
             <xm:f>その他!$B$3:$B$6</xm:f>
           </x14:formula1>
-          <xm:sqref>G127:G128 G130:G1048576 G1:G26 G28:G122</xm:sqref>
+          <xm:sqref>G126:G127 G129:G1048576 G1:G26 G28:G121</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{66D8840C-D443-486F-BC72-01200775D285}">
           <x14:formula1>
             <xm:f>その他!$D$3:$D$6</xm:f>
           </x14:formula1>
-          <xm:sqref>F127:F128 F130:F1048576 F1:F26 F28:F122</xm:sqref>
+          <xm:sqref>F126:F127 F129:F1048576 F1:F26 F28:F121</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{D61B1C0A-2748-4606-B0EE-00EEC89A23C6}">
           <x14:formula1>
             <xm:f>その他!$F$3:$F$6</xm:f>
           </x14:formula1>
-          <xm:sqref>E127:E128 E130:E1048576 E1:E26 E28:E122</xm:sqref>
+          <xm:sqref>E126:E127 E129:E1048576 E1:E26 E28:E121</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -4322,7 +4301,7 @@
       </c>
       <c r="J2" s="29">
         <f>SUM(C:C)</f>
-        <v>181.5</v>
+        <v>181</v>
       </c>
       <c r="K2" s="29"/>
       <c r="L2" s="28"/>
@@ -4357,7 +4336,7 @@
       </c>
       <c r="J3" s="29">
         <f>SUMIF(コスト表!G:G,"完了",コスト表!D:D)</f>
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="K3" s="28" t="s">
         <v>22</v>
@@ -4393,11 +4372,11 @@
       </c>
       <c r="J4" s="29">
         <f ca="1">NETWORKDAYS(J5,J6)</f>
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="K4" s="29">
         <f ca="1" xml:space="preserve"> ROUNDDOWN(J3 / J4,1)</f>
-        <v>1.9</v>
+        <v>1.7</v>
       </c>
       <c r="M4" s="28"/>
     </row>
@@ -4465,7 +4444,7 @@
       </c>
       <c r="J6" s="46">
         <f ca="1">TODAY()</f>
-        <v>45855</v>
+        <v>45866</v>
       </c>
       <c r="K6" s="46"/>
       <c r="L6" s="28"/>
@@ -4563,11 +4542,11 @@
       </c>
       <c r="K9" s="57">
         <f ca="1">NETWORKDAYS(TODAY(),J9)</f>
-        <v>5</v>
+        <v>-4</v>
       </c>
       <c r="L9" s="59">
         <f ca="1">ROUNDDOWN(($J$2-$J$3)/K9, 1)</f>
-        <v>14.9</v>
+        <v>-17.7</v>
       </c>
     </row>
     <row r="10" spans="2:13" ht="19.5">
@@ -4603,11 +4582,11 @@
       </c>
       <c r="K10" s="58">
         <f ca="1">NETWORKDAYS(TODAY(),J10)</f>
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="L10" s="60">
         <f ca="1">ROUNDDOWN(($J$2 - $J$3) / K10,1)</f>
-        <v>4.5999999999999996</v>
+        <v>7.8</v>
       </c>
     </row>
     <row r="11" spans="2:13" ht="19.5">
@@ -4620,11 +4599,11 @@
       </c>
       <c r="D11" s="51">
         <f>SUMIFS(コスト表!D:D, コスト表!B:B, "アイテム", コスト表!G:G, "完了")</f>
-        <v>8</v>
+        <v>8.5</v>
       </c>
       <c r="E11" s="51">
         <f>SUMIFS(コスト表!D:D, コスト表!B:B, "アイテム", コスト表!G:G, "作業中")</f>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="F11" s="51">
         <f>SUMIFS(コスト表!D:D, コスト表!B:B, "アイテム", コスト表!G:G, "未着手")</f>
@@ -4632,7 +4611,7 @@
       </c>
       <c r="G11" s="40">
         <f>ROUNDDOWN(COUNTIFS(コスト表!B:B, "アイテム", コスト表!G:G, "完了") / COUNTIF(コスト表!B:B, "アイテム") * 100,1)</f>
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="I11" s="31" t="s">
         <v>29</v>
@@ -4643,11 +4622,11 @@
       </c>
       <c r="K11" s="58">
         <f ca="1">NETWORKDAYS(TODAY(),J11)</f>
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="L11" s="60">
         <f ca="1">ROUNDDOWN(($J$2 - $J$3) / K11,1)</f>
-        <v>3.5</v>
+        <v>5</v>
       </c>
     </row>
     <row r="12" spans="2:13" ht="19.5">
@@ -4660,19 +4639,19 @@
       </c>
       <c r="D12" s="51">
         <f>SUMIFS(コスト表!D:D, コスト表!B:B, "タイトル", コスト表!G:G, "完了")</f>
-        <v>0.5</v>
+        <v>2</v>
       </c>
       <c r="E12" s="51">
         <f>SUMIFS(コスト表!D:D, コスト表!B:B, "タイトル", コスト表!G:G, "作業中")</f>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="F12" s="51">
         <f>SUMIFS(コスト表!D:D, コスト表!B:B, "タイトル", コスト表!G:G, "未着手")</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G12" s="40">
         <f>ROUNDDOWN(COUNTIFS(コスト表!B:B, "タイトル", コスト表!G:G, "完了") / COUNTIF(コスト表!B:B, "タイトル") * 100,1)</f>
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="I12" s="56" t="s">
         <v>30</v>
@@ -4683,11 +4662,11 @@
       </c>
       <c r="K12" s="58">
         <f ca="1">NETWORKDAYS(TODAY(),J12)</f>
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="L12" s="60">
         <f ca="1">ROUNDDOWN(($J$2 - $J$3) / K12,1)</f>
-        <v>2.2000000000000002</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="13" spans="2:13">
@@ -4700,11 +4679,11 @@
       </c>
       <c r="D13" s="51">
         <f>SUMIFS(コスト表!D:D, コスト表!B:B, "リザルト", コスト表!G:G, "完了")</f>
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="E13" s="51">
         <f>SUMIFS(コスト表!D:D, コスト表!B:B, "リザルト", コスト表!G:G, "作業中")</f>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="F13" s="51">
         <f>SUMIFS(コスト表!D:D, コスト表!B:B, "リザルト", コスト表!G:G, "未着手")</f>
@@ -4712,7 +4691,7 @@
       </c>
       <c r="G13" s="40">
         <f>ROUNDDOWN(COUNTIFS(コスト表!B:B, "リザルト", コスト表!G:G, "完了") / COUNTIF(コスト表!B:B, "リザルト") * 100,1)</f>
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="J13" s="46"/>
       <c r="K13" s="44"/>
@@ -4761,38 +4740,38 @@
       </c>
       <c r="C15" s="66">
         <f>SUMIF(コスト表!B:B, B15, コスト表!D:D)</f>
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="D15" s="66">
         <f>SUMIFS(コスト表!D:D, コスト表!B:B, "ゲームオーバー", コスト表!G:G, "完了")</f>
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="E15" s="66">
         <f>SUMIFS(コスト表!D:D, コスト表!B:B, "ゲームオーバー", コスト表!G:G, "作業中")</f>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="F15" s="66">
         <f>SUMIFS(コスト表!D:D, コスト表!B:B, "ゲームオーバー", コスト表!G:G, "未着手")</f>
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="G15" s="43">
         <f>ROUNDDOWN(COUNTIFS(コスト表!B:B, "ゲームオーバー", コスト表!G:G, "完了") / COUNTIF(コスト表!B:B, "ゲームオーバー") * 100,1)</f>
-        <v>40</v>
+        <v>75</v>
       </c>
       <c r="I15" s="43" t="s">
         <v>9</v>
       </c>
       <c r="J15" s="43">
         <f>SUMIF(コスト表!F:F, "プロト", コスト表!D:D)</f>
-        <v>126</v>
+        <v>125.5</v>
       </c>
       <c r="K15" s="43">
         <f>SUMIFS(コスト表!D:D, コスト表!F:F, "プロト", コスト表!G:G, "完了")</f>
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="L15" s="43">
         <f>ROUNDDOWN(COUNTIFS(コスト表!F:F, "プロト", コスト表!G:G, "完了") / COUNTIF(コスト表!F:F, "プロト") * 100,1)</f>
-        <v>65</v>
+        <v>72.8</v>
       </c>
     </row>
     <row r="16" spans="2:13">
@@ -4805,7 +4784,7 @@
       <c r="F16" s="9"/>
       <c r="G16" s="40">
         <f>ROUNDDOWN(COUNTIF(コスト表!G:G, "完了") / COUNTA(コスト表!G:G) * 100,1)</f>
-        <v>55.2</v>
+        <v>61</v>
       </c>
       <c r="I16" s="43" t="s">
         <v>12</v>
@@ -4833,11 +4812,11 @@
       </c>
       <c r="K17" s="43">
         <f>SUMIFS(コスト表!D:D, コスト表!F:F, "ベータ", コスト表!G:G, "完了")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L17" s="43">
         <f>ROUNDDOWN(COUNTIFS(コスト表!F:F, "ベータ", コスト表!G:G, "完了") / COUNTIF(コスト表!F:F, "ベータ") * 100,1)</f>
-        <v>0</v>
+        <v>50</v>
       </c>
     </row>
     <row r="18" spans="3:12">
@@ -4995,6 +4974,21 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="ドキュメント" ma:contentTypeID="0x0101006836AD0B55474E4CAD520F1DEB8FB579" ma:contentTypeVersion="3" ma:contentTypeDescription="新しいドキュメントを作成します。" ma:contentTypeScope="" ma:versionID="078ba6c1f7b5b638bb57eb024ae572f7">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="187a6309-4c0c-49e3-bd2d-e8130eb88270" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="c5f182963113af090d1b42042cf04cb6" ns2:_="">
     <xsd:import namespace="187a6309-4c0c-49e3-bd2d-e8130eb88270"/>
@@ -5132,22 +5126,24 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BC0DB335-AD01-472D-90D0-5B4B126AC491}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E90E09EE-5F6D-4AB8-AE54-C74368FE6F4B}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5A1D85CE-B20E-4841-A55B-779E85453EF9}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -5163,21 +5159,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E90E09EE-5F6D-4AB8-AE54-C74368FE6F4B}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BC0DB335-AD01-472D-90D0-5B4B126AC491}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/ゾンビシューターゲームコスト表.xlsx
+++ b/ゾンビシューターゲームコスト表.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sho24\OneDrive\ドキュメント\MyGame3D2\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\由留部 瑛人.FICPCROOMB14\Documents\GitHub\MyGame3D2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{975B0F2C-61C8-4863-AC78-ECC6AF9AD5B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{13F0E57A-DBD4-4D52-9BA3-401A4B37EB09}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4170" yWindow="1155" windowWidth="21600" windowHeight="11295" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3720" yWindow="2520" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="コスト表" sheetId="1" r:id="rId1"/>
     <sheet name="分類別コスト集計" sheetId="2" r:id="rId2"/>
-    <sheet name="その他" sheetId="3" r:id="rId3"/>
+    <sheet name="プルダウン用" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">コスト表!$E$2:$G$132</definedName>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="557" uniqueCount="159">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="433" uniqueCount="137">
   <si>
     <t>分類</t>
   </si>
@@ -71,18 +71,12 @@
     <t>S</t>
   </si>
   <si>
-    <t>プロト</t>
-  </si>
-  <si>
     <t>未着手</t>
   </si>
   <si>
     <t>B</t>
   </si>
   <si>
-    <t>アルファ</t>
-  </si>
-  <si>
     <t>作業中</t>
   </si>
   <si>
@@ -95,12 +89,6 @@
     <t>進捗段階</t>
   </si>
   <si>
-    <t>ベータ</t>
-  </si>
-  <si>
-    <t>マスター</t>
-  </si>
-  <si>
     <t>C</t>
   </si>
   <si>
@@ -122,60 +110,11 @@
     <t>今日の日付</t>
   </si>
   <si>
-    <t>残り日数(土日除く)</t>
-  </si>
-  <si>
-    <t>一日の消費コスト</t>
-  </si>
-  <si>
-    <t>理想</t>
-  </si>
-  <si>
-    <t>デッドライン</t>
-  </si>
-  <si>
-    <t>真実のデッドライン</t>
-  </si>
-  <si>
-    <t>ジャンプ</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>プレイヤー</t>
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>ダッシュ</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>wasd移動</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>歩きアニメーション</t>
-    <rPh sb="0" eb="1">
-      <t>アル</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>ダッシュアニメーション</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>ジャンプアニメーション</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>死亡アニメーション</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>体力</t>
-    <rPh sb="0" eb="2">
-      <t>タイリョク</t>
-    </rPh>
     <phoneticPr fontId="1"/>
   </si>
   <si>
@@ -249,13 +188,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>ドロップアイテム取得</t>
-    <rPh sb="8" eb="10">
-      <t>シュトク</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>タイトル</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -298,32 +230,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>一人称視点</t>
-    <rPh sb="0" eb="3">
-      <t>イチニンショウ</t>
-    </rPh>
-    <rPh sb="3" eb="5">
-      <t>シテン</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>K2作品フィードバック会(α版まで完成)</t>
-    <rPh sb="2" eb="4">
-      <t>サクヒン</t>
-    </rPh>
-    <rPh sb="11" eb="12">
-      <t>カイ</t>
-    </rPh>
-    <rPh sb="14" eb="15">
-      <t>バン</t>
-    </rPh>
-    <rPh sb="17" eb="19">
-      <t>カンセイ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>進捗率 (%)</t>
   </si>
   <si>
@@ -576,32 +482,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>クロスヘア</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>弾の発射音・武器切り替え音・空打ち音・足音・ジャンプ音・ダッシュ音・被弾音・死亡音</t>
-    <rPh sb="0" eb="1">
-      <t>タマ</t>
-    </rPh>
-    <rPh sb="4" eb="5">
-      <t>オト</t>
-    </rPh>
-    <rPh sb="6" eb="8">
-      <t>ブキ</t>
-    </rPh>
-    <rPh sb="8" eb="9">
-      <t>キ</t>
-    </rPh>
-    <rPh sb="10" eb="11">
-      <t>カ</t>
-    </rPh>
-    <rPh sb="12" eb="13">
-      <t>オト</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>完了コスト</t>
     <rPh sb="0" eb="2">
       <t>カンリョウ</t>
@@ -609,30 +489,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>ヘッドショット判定</t>
-    <rPh sb="7" eb="9">
-      <t>ハンテイ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>ヒットマーカー</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>弾が敵に当たった時に表示される視覚的なフィードバック、ダメージ量に応じた表示変化</t>
-    <rPh sb="31" eb="32">
-      <t>リョウ</t>
-    </rPh>
-    <rPh sb="33" eb="34">
-      <t>オウ</t>
-    </rPh>
-    <rPh sb="36" eb="40">
-      <t>ヒョウジヘンカ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>HP・攻撃力・移動速度など</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -651,10 +507,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>プロト</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>攻撃パターン実装</t>
     <rPh sb="0" eb="2">
       <t>コウゲキ</t>
@@ -749,26 +601,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>弾の発射処理</t>
-    <rPh sb="0" eb="1">
-      <t>タマ</t>
-    </rPh>
-    <rPh sb="2" eb="4">
-      <t>ハッシャ</t>
-    </rPh>
-    <rPh sb="4" eb="6">
-      <t>ショリ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>Rayを飛ばして判定</t>
-    <rPh sb="8" eb="10">
-      <t>ハンテイ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>当たり判定実装</t>
     <rPh sb="0" eb="1">
       <t>ア</t>
@@ -830,10 +662,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>死亡</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>作業中コスト</t>
     <rPh sb="0" eb="2">
       <t>サギョウ</t>
@@ -889,23 +717,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>ゲーム大祭日程：8/22</t>
-    <rPh sb="3" eb="5">
-      <t>タイサイ</t>
-    </rPh>
-    <rPh sb="5" eb="7">
-      <t>ニッテイ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>タックル攻撃</t>
-    <rPh sb="4" eb="6">
-      <t>コウゲキ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>タックル攻撃アニメーション</t>
     <rPh sb="4" eb="6">
       <t>コウゲキ</t>
@@ -913,23 +724,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>素材がない…</t>
-    <rPh sb="0" eb="2">
-      <t>ソザイ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>当たり判定</t>
-    <rPh sb="0" eb="1">
-      <t>ア</t>
-    </rPh>
-    <rPh sb="3" eb="5">
-      <t>ハンテイ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>プレイヤー</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -972,22 +766,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>射撃時画面ブレ効果</t>
-    <rPh sb="0" eb="2">
-      <t>シャゲキ</t>
-    </rPh>
-    <rPh sb="2" eb="3">
-      <t>ジ</t>
-    </rPh>
-    <rPh sb="3" eb="5">
-      <t>ガメン</t>
-    </rPh>
-    <rPh sb="7" eb="9">
-      <t>コウカ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>難易度調整</t>
     <rPh sb="3" eb="5">
       <t>チョウセイ</t>
@@ -1000,6 +778,91 @@
       <t>ケッカ</t>
     </rPh>
     <rPh sb="4" eb="6">
+      <t>ジッソウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>11月</t>
+    <rPh sb="2" eb="3">
+      <t>ガツ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>12月</t>
+    <rPh sb="2" eb="3">
+      <t>ガツ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>1月</t>
+    <rPh sb="1" eb="2">
+      <t>ガツ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ジャンプ時の画面効果</t>
+    <rPh sb="4" eb="5">
+      <t>ジ</t>
+    </rPh>
+    <rPh sb="6" eb="10">
+      <t>ガメンコウカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>10月</t>
+    <rPh sb="2" eb="3">
+      <t>ガツ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>死亡演出</t>
+    <rPh sb="0" eb="4">
+      <t>シボウエンシュツ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>方向インジケーター</t>
+    <rPh sb="0" eb="2">
+      <t>ホウコウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>クロスヘア</t>
+  </si>
+  <si>
+    <t>剣から盾にモデル変更</t>
+    <rPh sb="0" eb="1">
+      <t>ケン</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>タテ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>ヘンコウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ガード実装</t>
+    <rPh sb="3" eb="5">
+      <t>ジッソウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>耐久値実装</t>
+    <rPh sb="0" eb="3">
+      <t>タイキュウチ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
       <t>ジッソウ</t>
     </rPh>
     <phoneticPr fontId="1"/>
@@ -1009,7 +872,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="17">
+  <fonts count="12">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1094,52 +957,9 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="游ゴシック"/>
-      <family val="2"/>
-      <charset val="128"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="游ゴシック"/>
       <family val="3"/>
       <charset val="128"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="14"/>
-      <color theme="1"/>
-      <name val="游ゴシック"/>
-      <family val="3"/>
-      <charset val="128"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFC00000"/>
-      <name val="游ゴシック"/>
-      <family val="3"/>
-      <charset val="128"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFA20000"/>
-      <name val="Yu Gothic"/>
-      <family val="3"/>
-      <charset val="128"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="Yu Gothic"/>
-      <family val="3"/>
-      <charset val="128"/>
     </font>
     <font>
       <b/>
@@ -1150,7 +970,7 @@
       <charset val="128"/>
     </font>
   </fonts>
-  <fills count="12">
+  <fills count="11">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1191,12 +1011,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFD0CECE"/>
         <bgColor rgb="FF000000"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
@@ -1429,7 +1243,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="67">
+  <cellXfs count="57">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1488,12 +1302,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1539,7 +1347,7 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1554,7 +1362,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1588,36 +1396,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1">
+    <xf numFmtId="0" fontId="10" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="56" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="56" fontId="15" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="11" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="16" fillId="9" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="8" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
@@ -1978,30 +1762,30 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:8" ht="15.75" customHeight="1">
-      <c r="B1" s="54" t="s">
-        <v>77</v>
+      <c r="B1" s="52" t="s">
+        <v>58</v>
       </c>
     </row>
     <row r="2" spans="2:8" ht="18.75">
-      <c r="B2" s="24" t="s">
+      <c r="B2" s="22" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="25" t="s">
+      <c r="C2" s="23" t="s">
         <v>1</v>
       </c>
-      <c r="D2" s="26" t="s">
+      <c r="D2" s="24" t="s">
         <v>2</v>
       </c>
-      <c r="E2" s="25" t="s">
+      <c r="E2" s="23" t="s">
         <v>3</v>
       </c>
-      <c r="F2" s="27" t="s">
+      <c r="F2" s="25" t="s">
         <v>4</v>
       </c>
-      <c r="G2" s="27" t="s">
+      <c r="G2" s="25" t="s">
         <v>5</v>
       </c>
-      <c r="H2" s="27" t="s">
+      <c r="H2" s="25" t="s">
         <v>6</v>
       </c>
     </row>
@@ -2010,7 +1794,7 @@
         <v>7</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>34</v>
+        <v>129</v>
       </c>
       <c r="D3" s="8">
         <v>0.5</v>
@@ -2019,10 +1803,10 @@
         <v>8</v>
       </c>
       <c r="F3" s="10" t="s">
-        <v>9</v>
+        <v>130</v>
       </c>
       <c r="G3" s="10" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H3" s="14"/>
     </row>
@@ -2031,40 +1815,40 @@
         <v>7</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>33</v>
+        <v>131</v>
       </c>
       <c r="D4" s="7">
         <v>0.5</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="F4" s="11" t="s">
-        <v>9</v>
+        <v>130</v>
       </c>
       <c r="G4" s="11" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H4" s="15"/>
     </row>
     <row r="5" spans="2:8" ht="18.75">
       <c r="B5" s="1" t="s">
-        <v>100</v>
+        <v>81</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>156</v>
+        <v>28</v>
       </c>
       <c r="D5" s="7">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="F5" s="11" t="s">
-        <v>12</v>
+        <v>130</v>
       </c>
       <c r="G5" s="11" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="H5" s="15"/>
     </row>
@@ -2073,19 +1857,19 @@
         <v>7</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>31</v>
+        <v>132</v>
       </c>
       <c r="D6" s="7">
-        <v>0.5</v>
+        <v>2</v>
       </c>
       <c r="E6" s="5" t="s">
         <v>8</v>
       </c>
       <c r="F6" s="11" t="s">
-        <v>9</v>
+        <v>130</v>
       </c>
       <c r="G6" s="11" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H6" s="15"/>
     </row>
@@ -2094,19 +1878,19 @@
         <v>7</v>
       </c>
       <c r="C7" s="15" t="s">
-        <v>149</v>
+        <v>60</v>
       </c>
       <c r="D7" s="7">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E7" s="5" t="s">
         <v>8</v>
       </c>
       <c r="F7" s="11" t="s">
+        <v>126</v>
+      </c>
+      <c r="G7" s="11" t="s">
         <v>9</v>
-      </c>
-      <c r="G7" s="11" t="s">
-        <v>14</v>
       </c>
     </row>
     <row r="8" spans="2:8" ht="18.75">
@@ -2114,40 +1898,40 @@
         <v>7</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>39</v>
+        <v>61</v>
       </c>
       <c r="D8" s="7">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="E8" s="5" t="s">
         <v>8</v>
       </c>
       <c r="F8" s="11" t="s">
+        <v>126</v>
+      </c>
+      <c r="G8" s="11" t="s">
         <v>9</v>
-      </c>
-      <c r="G8" s="11" t="s">
-        <v>14</v>
       </c>
       <c r="H8" s="15"/>
     </row>
     <row r="9" spans="2:8" ht="18.75">
       <c r="B9" s="1" t="s">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>64</v>
+        <v>133</v>
       </c>
       <c r="D9" s="7">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="F9" s="11" t="s">
-        <v>9</v>
+        <v>130</v>
       </c>
       <c r="G9" s="11" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H9" s="15"/>
     </row>
@@ -2156,7 +1940,7 @@
         <v>7</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>139</v>
+        <v>43</v>
       </c>
       <c r="D10" s="7">
         <v>1</v>
@@ -2165,63 +1949,61 @@
         <v>8</v>
       </c>
       <c r="F10" s="11" t="s">
+        <v>127</v>
+      </c>
+      <c r="G10" s="11" t="s">
         <v>9</v>
-      </c>
-      <c r="G10" s="11" t="s">
-        <v>14</v>
       </c>
       <c r="H10" s="15"/>
     </row>
     <row r="11" spans="2:8" ht="18.75">
       <c r="B11" s="1" t="s">
-        <v>153</v>
+        <v>121</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>152</v>
+        <v>134</v>
       </c>
       <c r="D11" s="7">
-        <v>5</v>
+        <v>0.5</v>
       </c>
       <c r="E11" s="5" t="s">
         <v>8</v>
       </c>
       <c r="F11" s="11" t="s">
-        <v>9</v>
+        <v>126</v>
       </c>
       <c r="G11" s="11" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H11" s="15"/>
     </row>
     <row r="12" spans="2:8" ht="18.75">
       <c r="B12" s="1" t="s">
-        <v>78</v>
+        <v>59</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>79</v>
+        <v>135</v>
       </c>
       <c r="D12" s="7">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="F12" s="11" t="s">
-        <v>9</v>
+        <v>126</v>
       </c>
       <c r="G12" s="11" t="s">
-        <v>10</v>
-      </c>
-      <c r="H12" s="15" t="s">
-        <v>151</v>
-      </c>
+        <v>12</v>
+      </c>
+      <c r="H12" s="15"/>
     </row>
     <row r="13" spans="2:8" ht="18.75">
       <c r="B13" s="1" t="s">
-        <v>78</v>
+        <v>59</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>124</v>
+        <v>136</v>
       </c>
       <c r="D13" s="7">
         <v>1</v>
@@ -2230,162 +2012,88 @@
         <v>8</v>
       </c>
       <c r="F13" s="11" t="s">
-        <v>9</v>
+        <v>126</v>
       </c>
       <c r="G13" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="H13" s="15" t="s">
-        <v>125</v>
-      </c>
+        <v>12</v>
+      </c>
+      <c r="H13" s="15"/>
     </row>
     <row r="14" spans="2:8" ht="18.75">
       <c r="B14" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C14" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="D14" s="7">
-        <v>4</v>
-      </c>
-      <c r="E14" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="F14" s="11" t="s">
-        <v>9</v>
-      </c>
-      <c r="G14" s="11" t="s">
-        <v>14</v>
-      </c>
+      <c r="C14" s="1"/>
+      <c r="D14" s="7"/>
+      <c r="E14" s="5"/>
+      <c r="F14" s="11"/>
+      <c r="G14" s="11"/>
       <c r="H14" s="15"/>
     </row>
     <row r="15" spans="2:8" ht="18.75">
       <c r="B15" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="C15" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="D15" s="7">
-        <v>0.5</v>
-      </c>
-      <c r="E15" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="F15" s="11" t="s">
-        <v>9</v>
-      </c>
-      <c r="G15" s="11" t="s">
-        <v>14</v>
-      </c>
+        <v>81</v>
+      </c>
+      <c r="C15" s="1"/>
+      <c r="D15" s="7"/>
+      <c r="E15" s="5"/>
+      <c r="F15" s="11"/>
+      <c r="G15" s="11"/>
       <c r="H15" s="15"/>
     </row>
     <row r="16" spans="2:8" ht="18.75">
       <c r="B16" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="C16" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="D16" s="7">
-        <v>2</v>
-      </c>
-      <c r="E16" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="F16" s="11" t="s">
-        <v>9</v>
-      </c>
-      <c r="G16" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="H16" s="15" t="s">
-        <v>102</v>
-      </c>
+        <v>81</v>
+      </c>
+      <c r="C16" s="1"/>
+      <c r="D16" s="7"/>
+      <c r="E16" s="5"/>
+      <c r="F16" s="11"/>
+      <c r="G16" s="11"/>
+      <c r="H16" s="15"/>
     </row>
     <row r="17" spans="2:8" ht="18.75">
       <c r="B17" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="C17" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="D17" s="7">
-        <v>3</v>
-      </c>
-      <c r="E17" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="F17" s="11" t="s">
-        <v>9</v>
-      </c>
-      <c r="G17" s="11" t="s">
-        <v>14</v>
-      </c>
+        <v>81</v>
+      </c>
+      <c r="C17" s="1"/>
+      <c r="D17" s="7"/>
+      <c r="E17" s="5"/>
+      <c r="F17" s="11"/>
+      <c r="G17" s="11"/>
       <c r="H17" s="15"/>
     </row>
     <row r="18" spans="2:8" ht="18.75">
       <c r="B18" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C18" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="D18" s="7">
-        <v>0.5</v>
-      </c>
-      <c r="E18" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="F18" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="G18" s="11" t="s">
-        <v>14</v>
-      </c>
+      <c r="C18" s="1"/>
+      <c r="D18" s="7"/>
+      <c r="E18" s="5"/>
+      <c r="F18" s="11"/>
+      <c r="G18" s="11"/>
       <c r="H18" s="15"/>
     </row>
     <row r="19" spans="2:8" ht="18.75">
       <c r="B19" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C19" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="D19" s="7">
-        <v>0.5</v>
-      </c>
-      <c r="E19" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="F19" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="G19" s="11" t="s">
-        <v>14</v>
-      </c>
+      <c r="C19" s="1"/>
+      <c r="D19" s="7"/>
+      <c r="E19" s="5"/>
+      <c r="F19" s="11"/>
+      <c r="G19" s="11"/>
       <c r="H19" s="15"/>
     </row>
     <row r="20" spans="2:8" ht="18.75">
       <c r="B20" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C20" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="D20" s="7">
-        <v>0.5</v>
-      </c>
-      <c r="E20" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="F20" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="G20" s="11" t="s">
-        <v>14</v>
-      </c>
+      <c r="C20" s="1"/>
+      <c r="D20" s="7"/>
+      <c r="E20" s="5"/>
+      <c r="F20" s="11"/>
+      <c r="G20" s="11"/>
       <c r="H20" s="15"/>
     </row>
     <row r="21" spans="2:8" ht="18.75">
@@ -2393,7 +2101,7 @@
         <v>7</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>150</v>
+        <v>120</v>
       </c>
       <c r="D21" s="7">
         <v>0.5</v>
@@ -2401,11 +2109,9 @@
       <c r="E21" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="F21" s="11" t="s">
-        <v>12</v>
-      </c>
+      <c r="F21" s="11"/>
       <c r="G21" s="11" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H21" s="15"/>
     </row>
@@ -2414,7 +2120,7 @@
         <v>7</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>38</v>
+        <v>23</v>
       </c>
       <c r="D22" s="7">
         <v>0.5</v>
@@ -2422,11 +2128,9 @@
       <c r="E22" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="F22" s="11" t="s">
-        <v>12</v>
-      </c>
+      <c r="F22" s="11"/>
       <c r="G22" s="11" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H22" s="15"/>
     </row>
@@ -2435,7 +2139,7 @@
         <v>7</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>42</v>
+        <v>26</v>
       </c>
       <c r="D23" s="7">
         <v>0.5</v>
@@ -2443,94 +2147,60 @@
       <c r="E23" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="F23" s="11" t="s">
-        <v>12</v>
-      </c>
+      <c r="F23" s="11"/>
       <c r="G23" s="11" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H23" s="15"/>
     </row>
     <row r="24" spans="2:8" ht="18.75">
       <c r="B24" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="C24" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="D24" s="7">
-        <v>0.5</v>
-      </c>
-      <c r="E24" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="F24" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="G24" s="11" t="s">
-        <v>10</v>
-      </c>
+        <v>59</v>
+      </c>
+      <c r="C24" s="1"/>
+      <c r="D24" s="7"/>
+      <c r="E24" s="5"/>
+      <c r="F24" s="11"/>
+      <c r="G24" s="11"/>
       <c r="H24" s="15"/>
     </row>
     <row r="25" spans="2:8" ht="18.75">
       <c r="B25" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="C25" s="1" t="s">
-        <v>105</v>
-      </c>
-      <c r="D25" s="7">
-        <v>1</v>
-      </c>
-      <c r="E25" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="F25" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="G25" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="H25" s="49" t="s">
-        <v>106</v>
-      </c>
+        <v>81</v>
+      </c>
+      <c r="C25" s="1"/>
+      <c r="D25" s="7"/>
+      <c r="E25" s="5"/>
+      <c r="F25" s="11"/>
+      <c r="G25" s="11"/>
+      <c r="H25" s="47"/>
     </row>
     <row r="26" spans="2:8" ht="18.75">
       <c r="B26" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C26" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="D26" s="7">
-        <v>2</v>
-      </c>
-      <c r="E26" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="F26" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="G26" s="11" t="s">
-        <v>13</v>
-      </c>
+      <c r="C26" s="1"/>
+      <c r="D26" s="7"/>
+      <c r="E26" s="5"/>
+      <c r="F26" s="11"/>
+      <c r="G26" s="11"/>
       <c r="H26" s="5"/>
     </row>
     <row r="27" spans="2:8" ht="18.75">
-      <c r="B27" s="41"/>
-      <c r="C27" s="47"/>
-      <c r="D27" s="48"/>
-      <c r="E27" s="47"/>
-      <c r="F27" s="47"/>
-      <c r="G27" s="47"/>
+      <c r="B27" s="39"/>
+      <c r="C27" s="45"/>
+      <c r="D27" s="46"/>
+      <c r="E27" s="45"/>
+      <c r="F27" s="45"/>
+      <c r="G27" s="45"/>
       <c r="H27" s="6"/>
     </row>
     <row r="28" spans="2:8" ht="18.75">
       <c r="B28" s="3" t="s">
-        <v>138</v>
+        <v>111</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>83</v>
+        <v>64</v>
       </c>
       <c r="D28" s="8">
         <v>5</v>
@@ -2538,22 +2208,20 @@
       <c r="E28" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="F28" s="10" t="s">
-        <v>9</v>
-      </c>
+      <c r="F28" s="10"/>
       <c r="G28" s="10" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H28" s="14" t="s">
-        <v>84</v>
+        <v>65</v>
       </c>
     </row>
     <row r="29" spans="2:8" ht="18.75">
       <c r="B29" s="1" t="s">
-        <v>138</v>
+        <v>111</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>85</v>
+        <v>66</v>
       </c>
       <c r="D29" s="7">
         <v>4</v>
@@ -2561,22 +2229,20 @@
       <c r="E29" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="F29" s="11" t="s">
-        <v>9</v>
-      </c>
+      <c r="F29" s="11"/>
       <c r="G29" s="11" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H29" s="15" t="s">
-        <v>154</v>
+        <v>122</v>
       </c>
     </row>
     <row r="30" spans="2:8" ht="18.75">
       <c r="B30" s="1" t="s">
-        <v>138</v>
+        <v>111</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>86</v>
+        <v>67</v>
       </c>
       <c r="D30" s="7">
         <v>6</v>
@@ -2584,22 +2250,20 @@
       <c r="E30" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="F30" s="11" t="s">
-        <v>9</v>
-      </c>
+      <c r="F30" s="11"/>
       <c r="G30" s="11" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H30" s="15" t="s">
-        <v>155</v>
+        <v>123</v>
       </c>
     </row>
     <row r="31" spans="2:8" ht="18.75">
       <c r="B31" s="1" t="s">
-        <v>138</v>
+        <v>111</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>88</v>
+        <v>69</v>
       </c>
       <c r="D31" s="7">
         <v>2</v>
@@ -2607,20 +2271,18 @@
       <c r="E31" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="F31" s="11" t="s">
-        <v>9</v>
-      </c>
+      <c r="F31" s="11"/>
       <c r="G31" s="11" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H31" s="15"/>
     </row>
     <row r="32" spans="2:8" ht="18.75">
       <c r="B32" s="1" t="s">
-        <v>138</v>
+        <v>111</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>89</v>
+        <v>70</v>
       </c>
       <c r="D32" s="7">
         <v>4</v>
@@ -2628,22 +2290,20 @@
       <c r="E32" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="F32" s="11" t="s">
-        <v>12</v>
-      </c>
+      <c r="F32" s="11"/>
       <c r="G32" s="11" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H32" s="15" t="s">
-        <v>90</v>
+        <v>71</v>
       </c>
     </row>
     <row r="33" spans="2:8" ht="18.75">
       <c r="B33" s="1" t="s">
-        <v>138</v>
+        <v>111</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>91</v>
+        <v>72</v>
       </c>
       <c r="D33" s="7">
         <v>3</v>
@@ -2651,20 +2311,18 @@
       <c r="E33" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="F33" s="11" t="s">
-        <v>12</v>
-      </c>
+      <c r="F33" s="11"/>
       <c r="G33" s="11" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H33" s="15"/>
     </row>
     <row r="34" spans="2:8" ht="18.75">
       <c r="B34" s="1" t="s">
-        <v>138</v>
+        <v>111</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>108</v>
+        <v>84</v>
       </c>
       <c r="D34" s="7">
         <v>3</v>
@@ -2672,11 +2330,9 @@
       <c r="E34" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="F34" s="11" t="s">
-        <v>9</v>
-      </c>
+      <c r="F34" s="11"/>
       <c r="G34" s="11" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="H34" s="15"/>
     </row>
@@ -2691,10 +2347,10 @@
     </row>
     <row r="36" spans="2:8" ht="18.75">
       <c r="B36" s="1" t="s">
-        <v>40</v>
+        <v>24</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>95</v>
+        <v>76</v>
       </c>
       <c r="D36" s="4">
         <v>1.5</v>
@@ -2702,20 +2358,18 @@
       <c r="E36" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="F36" s="11" t="s">
-        <v>9</v>
-      </c>
+      <c r="F36" s="11"/>
       <c r="G36" s="11" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H36" s="15"/>
     </row>
     <row r="37" spans="2:8" ht="18.75">
       <c r="B37" s="1" t="s">
-        <v>40</v>
+        <v>24</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>93</v>
+        <v>74</v>
       </c>
       <c r="D37" s="7">
         <v>1</v>
@@ -2723,20 +2377,18 @@
       <c r="E37" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="F37" s="11" t="s">
-        <v>9</v>
-      </c>
+      <c r="F37" s="11"/>
       <c r="G37" s="11" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H37" s="15"/>
     </row>
     <row r="38" spans="2:8" ht="18.75">
       <c r="B38" s="1" t="s">
-        <v>40</v>
+        <v>24</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>92</v>
+        <v>73</v>
       </c>
       <c r="D38" s="7">
         <v>2</v>
@@ -2744,20 +2396,18 @@
       <c r="E38" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="F38" s="11" t="s">
-        <v>12</v>
-      </c>
+      <c r="F38" s="11"/>
       <c r="G38" s="11" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H38" s="15"/>
     </row>
     <row r="39" spans="2:8" ht="18.75">
       <c r="B39" s="1" t="s">
-        <v>40</v>
+        <v>24</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>120</v>
+        <v>95</v>
       </c>
       <c r="D39" s="7">
         <v>2</v>
@@ -2765,20 +2415,18 @@
       <c r="E39" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="F39" s="11" t="s">
-        <v>12</v>
-      </c>
+      <c r="F39" s="11"/>
       <c r="G39" s="11" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H39" s="15"/>
     </row>
     <row r="40" spans="2:8" ht="18.75">
       <c r="B40" s="1" t="s">
-        <v>40</v>
+        <v>24</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>126</v>
+        <v>99</v>
       </c>
       <c r="D40" s="7">
         <v>3</v>
@@ -2786,20 +2434,18 @@
       <c r="E40" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="F40" s="11" t="s">
-        <v>9</v>
-      </c>
+      <c r="F40" s="11"/>
       <c r="G40" s="11" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H40" s="15"/>
     </row>
     <row r="41" spans="2:8" ht="18.75">
       <c r="B41" s="1" t="s">
-        <v>40</v>
+        <v>24</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>109</v>
+        <v>85</v>
       </c>
       <c r="D41" s="7">
         <v>1</v>
@@ -2807,11 +2453,9 @@
       <c r="E41" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="F41" s="11" t="s">
-        <v>110</v>
-      </c>
+      <c r="F41" s="11"/>
       <c r="G41" s="11" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="H41" s="15"/>
     </row>
@@ -2826,10 +2470,10 @@
     </row>
     <row r="43" spans="2:8" ht="18.75">
       <c r="B43" s="3" t="s">
-        <v>41</v>
+        <v>25</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>94</v>
+        <v>75</v>
       </c>
       <c r="D43" s="8">
         <v>1</v>
@@ -2837,20 +2481,18 @@
       <c r="E43" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="F43" s="10" t="s">
-        <v>9</v>
-      </c>
+      <c r="F43" s="10"/>
       <c r="G43" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="H43" s="45"/>
+        <v>12</v>
+      </c>
+      <c r="H43" s="43"/>
     </row>
     <row r="44" spans="2:8" ht="18.75">
       <c r="B44" s="1" t="s">
-        <v>41</v>
+        <v>25</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>95</v>
+        <v>76</v>
       </c>
       <c r="D44" s="7">
         <v>1.5</v>
@@ -2858,20 +2500,18 @@
       <c r="E44" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="F44" s="11" t="s">
-        <v>9</v>
-      </c>
+      <c r="F44" s="11"/>
       <c r="G44" s="11" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H44" s="15"/>
     </row>
     <row r="45" spans="2:8" ht="18.75">
       <c r="B45" s="1" t="s">
-        <v>41</v>
+        <v>25</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>92</v>
+        <v>73</v>
       </c>
       <c r="D45" s="7">
         <v>2</v>
@@ -2879,20 +2519,18 @@
       <c r="E45" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="F45" s="11" t="s">
-        <v>12</v>
-      </c>
+      <c r="F45" s="11"/>
       <c r="G45" s="11" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H45" s="15"/>
     </row>
     <row r="46" spans="2:8" ht="18.75">
       <c r="B46" s="1" t="s">
-        <v>41</v>
+        <v>25</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>120</v>
+        <v>95</v>
       </c>
       <c r="D46" s="7">
         <v>2</v>
@@ -2900,20 +2538,18 @@
       <c r="E46" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="F46" s="11" t="s">
-        <v>12</v>
-      </c>
+      <c r="F46" s="11"/>
       <c r="G46" s="11" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H46" s="15"/>
     </row>
     <row r="47" spans="2:8" ht="18.75">
       <c r="B47" s="1" t="s">
-        <v>41</v>
+        <v>25</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>126</v>
+        <v>99</v>
       </c>
       <c r="D47" s="7">
         <v>3</v>
@@ -2921,20 +2557,18 @@
       <c r="E47" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="F47" s="11" t="s">
-        <v>9</v>
-      </c>
+      <c r="F47" s="11"/>
       <c r="G47" s="11" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H47" s="15"/>
     </row>
     <row r="48" spans="2:8" ht="18.75">
       <c r="B48" s="1" t="s">
-        <v>41</v>
+        <v>25</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>109</v>
+        <v>85</v>
       </c>
       <c r="D48" s="7">
         <v>1</v>
@@ -2942,11 +2576,9 @@
       <c r="E48" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="F48" s="11" t="s">
-        <v>9</v>
-      </c>
+      <c r="F48" s="11"/>
       <c r="G48" s="11" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="H48" s="15"/>
     </row>
@@ -2961,10 +2593,10 @@
     </row>
     <row r="50" spans="2:8" ht="18.75">
       <c r="B50" s="1" t="s">
-        <v>82</v>
+        <v>63</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>96</v>
+        <v>77</v>
       </c>
       <c r="D50" s="4">
         <v>1.5</v>
@@ -2972,20 +2604,18 @@
       <c r="E50" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="F50" s="11" t="s">
-        <v>9</v>
-      </c>
+      <c r="F50" s="11"/>
       <c r="G50" s="11" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H50" s="15"/>
     </row>
     <row r="51" spans="2:8" ht="18.75">
       <c r="B51" s="1" t="s">
-        <v>82</v>
+        <v>63</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>93</v>
+        <v>74</v>
       </c>
       <c r="D51" s="7">
         <v>1</v>
@@ -2993,20 +2623,18 @@
       <c r="E51" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="F51" s="11" t="s">
-        <v>9</v>
-      </c>
+      <c r="F51" s="11"/>
       <c r="G51" s="11" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H51" s="15"/>
     </row>
     <row r="52" spans="2:8" ht="18.75">
       <c r="B52" s="1" t="s">
-        <v>82</v>
+        <v>63</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>92</v>
+        <v>73</v>
       </c>
       <c r="D52" s="7">
         <v>2</v>
@@ -3014,20 +2642,18 @@
       <c r="E52" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="F52" s="11" t="s">
-        <v>12</v>
-      </c>
+      <c r="F52" s="11"/>
       <c r="G52" s="11" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H52" s="15"/>
     </row>
     <row r="53" spans="2:8" ht="18.75">
       <c r="B53" s="1" t="s">
-        <v>82</v>
+        <v>63</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>120</v>
+        <v>95</v>
       </c>
       <c r="D53" s="7">
         <v>2</v>
@@ -3035,20 +2661,18 @@
       <c r="E53" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="F53" s="11" t="s">
-        <v>12</v>
-      </c>
+      <c r="F53" s="11"/>
       <c r="G53" s="11" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H53" s="15"/>
     </row>
     <row r="54" spans="2:8" ht="18.75">
       <c r="B54" s="1" t="s">
-        <v>82</v>
+        <v>63</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>126</v>
+        <v>99</v>
       </c>
       <c r="D54" s="7">
         <v>3</v>
@@ -3056,20 +2680,18 @@
       <c r="E54" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="F54" s="11" t="s">
-        <v>9</v>
-      </c>
+      <c r="F54" s="11"/>
       <c r="G54" s="11" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H54" s="15"/>
     </row>
     <row r="55" spans="2:8" ht="18.75">
       <c r="B55" s="1" t="s">
-        <v>82</v>
+        <v>63</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>109</v>
+        <v>85</v>
       </c>
       <c r="D55" s="7">
         <v>1</v>
@@ -3077,11 +2699,9 @@
       <c r="E55" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="F55" s="11" t="s">
-        <v>9</v>
-      </c>
+      <c r="F55" s="11"/>
       <c r="G55" s="11" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="H55" s="15"/>
     </row>
@@ -3096,10 +2716,10 @@
     </row>
     <row r="57" spans="2:8" ht="18.75">
       <c r="B57" s="3" t="s">
-        <v>71</v>
+        <v>52</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>111</v>
+        <v>86</v>
       </c>
       <c r="D57" s="8">
         <v>5</v>
@@ -3107,20 +2727,18 @@
       <c r="E57" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="F57" s="10" t="s">
+      <c r="F57" s="10"/>
+      <c r="G57" s="10" t="s">
         <v>9</v>
-      </c>
-      <c r="G57" s="10" t="s">
-        <v>10</v>
       </c>
       <c r="H57" s="14"/>
     </row>
     <row r="58" spans="2:8" ht="18.75">
       <c r="B58" s="1" t="s">
-        <v>71</v>
+        <v>52</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>112</v>
+        <v>87</v>
       </c>
       <c r="D58" s="7">
         <v>4</v>
@@ -3128,20 +2746,18 @@
       <c r="E58" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="F58" s="11" t="s">
+      <c r="F58" s="11"/>
+      <c r="G58" s="11" t="s">
         <v>9</v>
-      </c>
-      <c r="G58" s="11" t="s">
-        <v>10</v>
       </c>
       <c r="H58" s="15"/>
     </row>
     <row r="59" spans="2:8" ht="18.75">
       <c r="B59" s="1" t="s">
-        <v>71</v>
+        <v>52</v>
       </c>
       <c r="C59" s="1" t="s">
-        <v>93</v>
+        <v>74</v>
       </c>
       <c r="D59" s="7">
         <v>1</v>
@@ -3149,20 +2765,18 @@
       <c r="E59" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="F59" s="11" t="s">
+      <c r="F59" s="11"/>
+      <c r="G59" s="11" t="s">
         <v>9</v>
-      </c>
-      <c r="G59" s="11" t="s">
-        <v>10</v>
       </c>
       <c r="H59" s="15"/>
     </row>
     <row r="60" spans="2:8" ht="18.75">
       <c r="B60" s="1" t="s">
-        <v>87</v>
+        <v>68</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>113</v>
+        <v>88</v>
       </c>
       <c r="D60" s="7">
         <v>5</v>
@@ -3170,22 +2784,20 @@
       <c r="E60" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="F60" s="11" t="s">
-        <v>12</v>
-      </c>
+      <c r="F60" s="11"/>
       <c r="G60" s="11" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H60" s="15" t="s">
-        <v>43</v>
+        <v>27</v>
       </c>
     </row>
     <row r="61" spans="2:8" ht="18.75">
       <c r="B61" s="1" t="s">
-        <v>71</v>
+        <v>52</v>
       </c>
       <c r="C61" s="1" t="s">
-        <v>92</v>
+        <v>73</v>
       </c>
       <c r="D61" s="7">
         <v>3</v>
@@ -3193,20 +2805,18 @@
       <c r="E61" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="F61" s="11" t="s">
-        <v>12</v>
-      </c>
+      <c r="F61" s="11"/>
       <c r="G61" s="11" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H61" s="15"/>
     </row>
     <row r="62" spans="2:8" ht="18.75">
       <c r="B62" s="1" t="s">
-        <v>71</v>
+        <v>52</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>120</v>
+        <v>95</v>
       </c>
       <c r="D62" s="7">
         <v>2</v>
@@ -3214,20 +2824,18 @@
       <c r="E62" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="F62" s="11" t="s">
-        <v>12</v>
-      </c>
+      <c r="F62" s="11"/>
       <c r="G62" s="11" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H62" s="15"/>
     </row>
     <row r="63" spans="2:8" ht="18.75">
       <c r="B63" s="1" t="s">
-        <v>71</v>
+        <v>52</v>
       </c>
       <c r="C63" s="1" t="s">
-        <v>126</v>
+        <v>99</v>
       </c>
       <c r="D63" s="7">
         <v>3</v>
@@ -3235,20 +2843,18 @@
       <c r="E63" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="F63" s="11" t="s">
+      <c r="F63" s="11"/>
+      <c r="G63" s="11" t="s">
         <v>9</v>
-      </c>
-      <c r="G63" s="11" t="s">
-        <v>10</v>
       </c>
       <c r="H63" s="15"/>
     </row>
     <row r="64" spans="2:8" ht="18.75">
       <c r="B64" s="1" t="s">
-        <v>71</v>
+        <v>52</v>
       </c>
       <c r="C64" s="1" t="s">
-        <v>109</v>
+        <v>85</v>
       </c>
       <c r="D64" s="7">
         <v>1</v>
@@ -3256,11 +2862,9 @@
       <c r="E64" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="F64" s="11" t="s">
+      <c r="F64" s="11"/>
+      <c r="G64" s="11" t="s">
         <v>9</v>
-      </c>
-      <c r="G64" s="11" t="s">
-        <v>10</v>
       </c>
       <c r="H64" s="15"/>
     </row>
@@ -3275,10 +2879,10 @@
     </row>
     <row r="66" spans="2:8" ht="18.75">
       <c r="B66" s="1" t="s">
-        <v>114</v>
+        <v>89</v>
       </c>
       <c r="C66" s="1" t="s">
-        <v>115</v>
+        <v>90</v>
       </c>
       <c r="D66" s="4">
         <v>2</v>
@@ -3286,20 +2890,18 @@
       <c r="E66" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="F66" s="11" t="s">
-        <v>9</v>
-      </c>
+      <c r="F66" s="11"/>
       <c r="G66" s="11" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H66" s="15"/>
     </row>
     <row r="67" spans="2:8" ht="18.75">
       <c r="B67" s="1" t="s">
-        <v>114</v>
+        <v>89</v>
       </c>
       <c r="C67" s="1" t="s">
-        <v>116</v>
+        <v>91</v>
       </c>
       <c r="D67" s="7">
         <v>2</v>
@@ -3307,20 +2909,18 @@
       <c r="E67" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="F67" s="11" t="s">
-        <v>9</v>
-      </c>
+      <c r="F67" s="11"/>
       <c r="G67" s="11" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H67" s="15"/>
     </row>
     <row r="68" spans="2:8" ht="18.75">
       <c r="B68" s="1" t="s">
-        <v>114</v>
+        <v>89</v>
       </c>
       <c r="C68" s="1" t="s">
-        <v>117</v>
+        <v>92</v>
       </c>
       <c r="D68" s="7">
         <v>2</v>
@@ -3328,20 +2928,18 @@
       <c r="E68" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="F68" s="11" t="s">
-        <v>9</v>
-      </c>
+      <c r="F68" s="11"/>
       <c r="G68" s="11" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H68" s="15"/>
     </row>
     <row r="69" spans="2:8" ht="18.75">
       <c r="B69" s="1" t="s">
-        <v>114</v>
+        <v>89</v>
       </c>
       <c r="C69" s="1" t="s">
-        <v>118</v>
+        <v>93</v>
       </c>
       <c r="D69" s="7">
         <v>2</v>
@@ -3349,11 +2947,9 @@
       <c r="E69" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="F69" s="11" t="s">
-        <v>9</v>
-      </c>
+      <c r="F69" s="11"/>
       <c r="G69" s="11" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H69" s="15"/>
     </row>
@@ -3368,10 +2964,10 @@
     </row>
     <row r="71" spans="2:8" ht="18.75">
       <c r="B71" s="3" t="s">
-        <v>123</v>
+        <v>98</v>
       </c>
       <c r="C71" s="3" t="s">
-        <v>45</v>
+        <v>29</v>
       </c>
       <c r="D71" s="4">
         <v>2</v>
@@ -3379,22 +2975,20 @@
       <c r="E71" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="F71" s="10" t="s">
-        <v>9</v>
-      </c>
+      <c r="F71" s="10"/>
       <c r="G71" s="10" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H71" s="14" t="s">
-        <v>46</v>
+        <v>30</v>
       </c>
     </row>
     <row r="72" spans="2:8" ht="18.75">
       <c r="B72" s="1" t="s">
-        <v>123</v>
+        <v>98</v>
       </c>
       <c r="C72" s="1" t="s">
-        <v>47</v>
+        <v>31</v>
       </c>
       <c r="D72" s="7">
         <v>2</v>
@@ -3402,20 +2996,18 @@
       <c r="E72" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="F72" s="11" t="s">
-        <v>9</v>
-      </c>
+      <c r="F72" s="11"/>
       <c r="G72" s="11" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H72" s="15"/>
     </row>
     <row r="73" spans="2:8" ht="18.75">
       <c r="B73" s="1" t="s">
-        <v>123</v>
+        <v>98</v>
       </c>
       <c r="C73" s="1" t="s">
-        <v>99</v>
+        <v>80</v>
       </c>
       <c r="D73" s="7">
         <v>4</v>
@@ -3423,20 +3015,18 @@
       <c r="E73" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="F73" s="11" t="s">
-        <v>9</v>
-      </c>
+      <c r="F73" s="11"/>
       <c r="G73" s="11" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H73" s="15"/>
     </row>
     <row r="74" spans="2:8" ht="18.75">
       <c r="B74" s="1" t="s">
-        <v>123</v>
+        <v>98</v>
       </c>
       <c r="C74" s="1" t="s">
-        <v>48</v>
+        <v>32</v>
       </c>
       <c r="D74" s="7">
         <v>4</v>
@@ -3444,22 +3034,20 @@
       <c r="E74" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="F74" s="11" t="s">
-        <v>9</v>
-      </c>
+      <c r="F74" s="11"/>
       <c r="G74" s="11" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H74" s="15" t="s">
-        <v>49</v>
+        <v>33</v>
       </c>
     </row>
     <row r="75" spans="2:8" ht="18.75">
       <c r="B75" s="1" t="s">
-        <v>123</v>
+        <v>98</v>
       </c>
       <c r="C75" s="1" t="s">
-        <v>50</v>
+        <v>34</v>
       </c>
       <c r="D75" s="7">
         <v>4</v>
@@ -3467,22 +3055,20 @@
       <c r="E75" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="F75" s="11" t="s">
-        <v>9</v>
-      </c>
+      <c r="F75" s="11"/>
       <c r="G75" s="11" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H75" s="15" t="s">
-        <v>121</v>
+        <v>96</v>
       </c>
     </row>
     <row r="76" spans="2:8" ht="18.75">
       <c r="B76" s="1" t="s">
-        <v>123</v>
+        <v>98</v>
       </c>
       <c r="C76" s="1" t="s">
-        <v>97</v>
+        <v>78</v>
       </c>
       <c r="D76" s="7">
         <v>6</v>
@@ -3490,22 +3076,20 @@
       <c r="E76" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="F76" s="11" t="s">
+      <c r="F76" s="11"/>
+      <c r="G76" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="G76" s="11" t="s">
-        <v>10</v>
-      </c>
       <c r="H76" s="15" t="s">
-        <v>107</v>
+        <v>83</v>
       </c>
     </row>
     <row r="77" spans="2:8" ht="18.75">
       <c r="B77" s="1" t="s">
-        <v>123</v>
+        <v>98</v>
       </c>
       <c r="C77" s="1" t="s">
-        <v>98</v>
+        <v>79</v>
       </c>
       <c r="D77" s="7">
         <v>3</v>
@@ -3513,20 +3097,18 @@
       <c r="E77" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="F77" s="11" t="s">
-        <v>12</v>
-      </c>
+      <c r="F77" s="11"/>
       <c r="G77" s="11" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="H77" s="15"/>
     </row>
     <row r="78" spans="2:8" ht="18.75">
       <c r="B78" s="1" t="s">
-        <v>123</v>
+        <v>98</v>
       </c>
       <c r="C78" s="1" t="s">
-        <v>157</v>
+        <v>124</v>
       </c>
       <c r="D78" s="7">
         <v>2</v>
@@ -3534,11 +3116,9 @@
       <c r="E78" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="F78" s="11" t="s">
-        <v>17</v>
-      </c>
+      <c r="F78" s="11"/>
       <c r="G78" s="11" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H78" s="15"/>
     </row>
@@ -3553,10 +3133,10 @@
     </row>
     <row r="80" spans="2:8" ht="18.75">
       <c r="B80" s="3" t="s">
-        <v>51</v>
+        <v>35</v>
       </c>
       <c r="C80" s="3" t="s">
-        <v>74</v>
+        <v>55</v>
       </c>
       <c r="D80" s="8">
         <v>2</v>
@@ -3564,20 +3144,18 @@
       <c r="E80" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="F80" s="10" t="s">
-        <v>9</v>
-      </c>
+      <c r="F80" s="10"/>
       <c r="G80" s="10" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H80" s="14"/>
     </row>
     <row r="81" spans="2:8" ht="18.75">
       <c r="B81" s="1" t="s">
-        <v>75</v>
+        <v>56</v>
       </c>
       <c r="C81" s="1" t="s">
-        <v>76</v>
+        <v>57</v>
       </c>
       <c r="D81" s="7">
         <v>2</v>
@@ -3585,20 +3163,18 @@
       <c r="E81" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="F81" s="11" t="s">
-        <v>9</v>
-      </c>
+      <c r="F81" s="11"/>
       <c r="G81" s="11" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H81" s="15"/>
     </row>
     <row r="82" spans="2:8" ht="18.75">
       <c r="B82" s="1" t="s">
-        <v>51</v>
+        <v>35</v>
       </c>
       <c r="C82" s="1" t="s">
-        <v>73</v>
+        <v>54</v>
       </c>
       <c r="D82" s="7">
         <v>2</v>
@@ -3606,20 +3182,18 @@
       <c r="E82" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="F82" s="11" t="s">
-        <v>12</v>
-      </c>
+      <c r="F82" s="11"/>
       <c r="G82" s="11" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H82" s="15"/>
     </row>
     <row r="83" spans="2:8" ht="18.75">
       <c r="B83" s="1" t="s">
-        <v>51</v>
+        <v>35</v>
       </c>
       <c r="C83" s="1" t="s">
-        <v>53</v>
+        <v>37</v>
       </c>
       <c r="D83" s="7">
         <v>2</v>
@@ -3627,20 +3201,18 @@
       <c r="E83" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="F83" s="11" t="s">
-        <v>12</v>
-      </c>
+      <c r="F83" s="11"/>
       <c r="G83" s="11" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H83" s="15"/>
     </row>
     <row r="84" spans="2:8" ht="18.75">
       <c r="B84" s="1" t="s">
-        <v>51</v>
+        <v>35</v>
       </c>
       <c r="C84" s="1" t="s">
-        <v>129</v>
+        <v>102</v>
       </c>
       <c r="D84" s="7">
         <v>0.5</v>
@@ -3648,11 +3220,9 @@
       <c r="E84" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="F84" s="11" t="s">
-        <v>9</v>
-      </c>
+      <c r="F84" s="11"/>
       <c r="G84" s="11" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H84" s="15"/>
     </row>
@@ -3667,10 +3237,10 @@
     </row>
     <row r="86" spans="2:8" ht="18.75">
       <c r="B86" s="1" t="s">
-        <v>55</v>
+        <v>38</v>
       </c>
       <c r="C86" s="1" t="s">
-        <v>56</v>
+        <v>39</v>
       </c>
       <c r="D86" s="4">
         <v>1</v>
@@ -3678,20 +3248,18 @@
       <c r="E86" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="F86" s="11" t="s">
-        <v>17</v>
-      </c>
+      <c r="F86" s="11"/>
       <c r="G86" s="11" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H86" s="15"/>
     </row>
     <row r="87" spans="2:8" ht="18.75">
       <c r="B87" s="1" t="s">
-        <v>55</v>
+        <v>38</v>
       </c>
       <c r="C87" s="1" t="s">
-        <v>57</v>
+        <v>40</v>
       </c>
       <c r="D87" s="7">
         <v>0.5</v>
@@ -3699,62 +3267,56 @@
       <c r="E87" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="F87" s="11" t="s">
-        <v>9</v>
-      </c>
+      <c r="F87" s="11"/>
       <c r="G87" s="11" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H87" s="15"/>
     </row>
     <row r="88" spans="2:8" ht="18.75">
       <c r="B88" s="1" t="s">
-        <v>55</v>
+        <v>38</v>
       </c>
       <c r="C88" s="1" t="s">
-        <v>58</v>
+        <v>41</v>
       </c>
       <c r="D88" s="7">
         <v>1</v>
       </c>
       <c r="E88" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="F88" s="11" t="s">
-        <v>12</v>
-      </c>
+        <v>13</v>
+      </c>
+      <c r="F88" s="11"/>
       <c r="G88" s="11" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H88" s="15"/>
     </row>
     <row r="89" spans="2:8" ht="18.75">
       <c r="B89" s="1" t="s">
-        <v>55</v>
+        <v>38</v>
       </c>
       <c r="C89" s="1" t="s">
-        <v>144</v>
+        <v>116</v>
       </c>
       <c r="D89" s="7">
         <v>1</v>
       </c>
       <c r="E89" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="F89" s="11" t="s">
-        <v>12</v>
-      </c>
+        <v>13</v>
+      </c>
+      <c r="F89" s="11"/>
       <c r="G89" s="11" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H89" s="15"/>
     </row>
     <row r="90" spans="2:8" ht="18.75">
       <c r="B90" s="1" t="s">
-        <v>55</v>
+        <v>38</v>
       </c>
       <c r="C90" s="1" t="s">
-        <v>129</v>
+        <v>102</v>
       </c>
       <c r="D90" s="7">
         <v>0.5</v>
@@ -3762,11 +3324,9 @@
       <c r="E90" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="F90" s="11" t="s">
-        <v>9</v>
-      </c>
+      <c r="F90" s="11"/>
       <c r="G90" s="11" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H90" s="15"/>
     </row>
@@ -3781,10 +3341,10 @@
     </row>
     <row r="92" spans="2:8" ht="18.75">
       <c r="B92" s="3" t="s">
-        <v>128</v>
+        <v>101</v>
       </c>
       <c r="C92" s="3" t="s">
-        <v>129</v>
+        <v>102</v>
       </c>
       <c r="D92" s="8">
         <v>0.5</v>
@@ -3792,20 +3352,18 @@
       <c r="E92" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="F92" s="10" t="s">
-        <v>9</v>
-      </c>
+      <c r="F92" s="10"/>
       <c r="G92" s="10" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H92" s="14"/>
     </row>
     <row r="93" spans="2:8" ht="18.75">
       <c r="B93" s="1" t="s">
-        <v>127</v>
+        <v>100</v>
       </c>
       <c r="C93" s="1" t="s">
-        <v>57</v>
+        <v>40</v>
       </c>
       <c r="D93" s="7">
         <v>0.5</v>
@@ -3813,79 +3371,71 @@
       <c r="E93" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="F93" s="11" t="s">
-        <v>9</v>
-      </c>
+      <c r="F93" s="11"/>
       <c r="G93" s="11" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H93" s="15"/>
     </row>
     <row r="94" spans="2:8" ht="18.75">
       <c r="B94" s="1" t="s">
-        <v>127</v>
+        <v>100</v>
       </c>
       <c r="C94" s="1" t="s">
-        <v>133</v>
+        <v>106</v>
       </c>
       <c r="D94" s="7">
         <v>1</v>
       </c>
       <c r="E94" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="F94" s="11" t="s">
-        <v>12</v>
-      </c>
+        <v>13</v>
+      </c>
+      <c r="F94" s="11"/>
       <c r="G94" s="11" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H94" s="15"/>
     </row>
     <row r="95" spans="2:8" ht="18.75">
       <c r="B95" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="C95" s="49" t="s">
-        <v>131</v>
+        <v>101</v>
+      </c>
+      <c r="C95" s="47" t="s">
+        <v>104</v>
       </c>
       <c r="D95" s="7">
         <v>1</v>
       </c>
       <c r="E95" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="F95" s="11" t="s">
-        <v>12</v>
-      </c>
+        <v>15</v>
+      </c>
+      <c r="F95" s="11"/>
       <c r="G95" s="11" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H95" s="15" t="s">
-        <v>132</v>
+        <v>105</v>
       </c>
     </row>
     <row r="96" spans="2:8" ht="18.75">
       <c r="B96" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="C96" s="53" t="s">
-        <v>158</v>
-      </c>
-      <c r="D96" s="52">
+        <v>101</v>
+      </c>
+      <c r="C96" s="51" t="s">
+        <v>125</v>
+      </c>
+      <c r="D96" s="50">
         <v>1</v>
       </c>
-      <c r="E96" s="52" t="s">
-        <v>8</v>
-      </c>
-      <c r="F96" s="52" t="s">
-        <v>12</v>
-      </c>
+      <c r="E96" s="50" t="s">
+        <v>8</v>
+      </c>
+      <c r="F96" s="50"/>
       <c r="G96" s="5" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H96" s="15" t="s">
-        <v>145</v>
+        <v>117</v>
       </c>
     </row>
     <row r="97" spans="2:8" ht="18.75">
@@ -3899,33 +3449,31 @@
     </row>
     <row r="98" spans="2:8" ht="18.75">
       <c r="B98" s="3" t="s">
-        <v>59</v>
+        <v>42</v>
       </c>
       <c r="C98" s="3" t="s">
-        <v>60</v>
+        <v>43</v>
       </c>
       <c r="D98" s="4">
         <v>2</v>
       </c>
       <c r="E98" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="F98" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F98" s="4"/>
+      <c r="G98" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="G98" s="10" t="s">
-        <v>10</v>
-      </c>
       <c r="H98" s="14" t="s">
-        <v>61</v>
+        <v>44</v>
       </c>
     </row>
     <row r="99" spans="2:8" ht="18.75">
       <c r="B99" s="1" t="s">
-        <v>59</v>
+        <v>42</v>
       </c>
       <c r="C99" s="1" t="s">
-        <v>62</v>
+        <v>45</v>
       </c>
       <c r="D99" s="7">
         <v>1</v>
@@ -3933,20 +3481,18 @@
       <c r="E99" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="F99" s="11" t="s">
+      <c r="F99" s="11"/>
+      <c r="G99" s="11" t="s">
         <v>9</v>
-      </c>
-      <c r="G99" s="11" t="s">
-        <v>10</v>
       </c>
       <c r="H99" s="15"/>
     </row>
     <row r="100" spans="2:8" ht="18.75">
       <c r="B100" s="1" t="s">
-        <v>59</v>
+        <v>42</v>
       </c>
       <c r="C100" s="1" t="s">
-        <v>63</v>
+        <v>46</v>
       </c>
       <c r="D100" s="7">
         <v>1</v>
@@ -3954,22 +3500,20 @@
       <c r="E100" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="F100" s="11" t="s">
+      <c r="F100" s="11"/>
+      <c r="G100" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="G100" s="11" t="s">
-        <v>10</v>
-      </c>
       <c r="H100" s="15" t="s">
-        <v>81</v>
+        <v>62</v>
       </c>
     </row>
     <row r="101" spans="2:8" ht="18.75">
       <c r="B101" s="1" t="s">
-        <v>59</v>
+        <v>42</v>
       </c>
       <c r="C101" s="1" t="s">
-        <v>57</v>
+        <v>40</v>
       </c>
       <c r="D101" s="7">
         <v>0.5</v>
@@ -3977,53 +3521,47 @@
       <c r="E101" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="F101" s="11" t="s">
+      <c r="F101" s="11"/>
+      <c r="G101" s="11" t="s">
         <v>9</v>
-      </c>
-      <c r="G101" s="11" t="s">
-        <v>10</v>
       </c>
       <c r="H101" s="15"/>
     </row>
     <row r="102" spans="2:8" ht="18.75">
       <c r="B102" s="1" t="s">
-        <v>59</v>
+        <v>42</v>
       </c>
       <c r="C102" s="1" t="s">
-        <v>58</v>
+        <v>41</v>
       </c>
       <c r="D102" s="7">
         <v>1</v>
       </c>
       <c r="E102" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="F102" s="11" t="s">
-        <v>12</v>
-      </c>
+        <v>13</v>
+      </c>
+      <c r="F102" s="11"/>
       <c r="G102" s="11" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H102" s="15"/>
     </row>
     <row r="103" spans="2:8" ht="18.75">
       <c r="B103" s="1" t="s">
-        <v>59</v>
+        <v>42</v>
       </c>
       <c r="C103" s="1" t="s">
-        <v>144</v>
+        <v>116</v>
       </c>
       <c r="D103" s="7">
         <v>1</v>
       </c>
       <c r="E103" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="F103" s="11" t="s">
-        <v>12</v>
-      </c>
+        <v>13</v>
+      </c>
+      <c r="F103" s="11"/>
       <c r="G103" s="11" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H103" s="15"/>
     </row>
@@ -4038,10 +3576,10 @@
     </row>
     <row r="105" spans="2:8" ht="18.75">
       <c r="B105" s="1" t="s">
-        <v>143</v>
+        <v>115</v>
       </c>
       <c r="C105" s="3" t="s">
-        <v>109</v>
+        <v>85</v>
       </c>
       <c r="D105" s="8">
         <v>0.5</v>
@@ -4049,20 +3587,18 @@
       <c r="E105" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="F105" s="10" t="s">
-        <v>9</v>
-      </c>
+      <c r="F105" s="10"/>
       <c r="G105" s="10" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H105" s="15"/>
     </row>
     <row r="106" spans="2:8" ht="18.75">
       <c r="B106" s="1" t="s">
-        <v>142</v>
+        <v>114</v>
       </c>
       <c r="C106" s="1" t="s">
-        <v>57</v>
+        <v>40</v>
       </c>
       <c r="D106" s="7">
         <v>0.5</v>
@@ -4070,56 +3606,50 @@
       <c r="E106" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="F106" s="11" t="s">
-        <v>9</v>
-      </c>
+      <c r="F106" s="11"/>
       <c r="G106" s="11" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H106" s="15"/>
     </row>
     <row r="107" spans="2:8" ht="18.75">
       <c r="B107" s="1" t="s">
-        <v>142</v>
+        <v>114</v>
       </c>
       <c r="C107" s="1" t="s">
-        <v>58</v>
+        <v>41</v>
       </c>
       <c r="D107" s="7">
         <v>1</v>
       </c>
       <c r="E107" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="F107" s="11" t="s">
-        <v>12</v>
-      </c>
+        <v>13</v>
+      </c>
+      <c r="F107" s="11"/>
       <c r="G107" s="11" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H107" s="15"/>
     </row>
     <row r="108" spans="2:8" ht="18.75">
       <c r="B108" s="1" t="s">
-        <v>142</v>
+        <v>114</v>
       </c>
       <c r="C108" s="1" t="s">
-        <v>144</v>
+        <v>116</v>
       </c>
       <c r="D108" s="7">
         <v>1</v>
       </c>
       <c r="E108" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="F108" s="11" t="s">
-        <v>12</v>
-      </c>
+        <v>13</v>
+      </c>
+      <c r="F108" s="11"/>
       <c r="G108" s="11" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H108" s="15" t="s">
-        <v>146</v>
+        <v>118</v>
       </c>
     </row>
     <row r="109" spans="2:8" ht="18.75">
@@ -4238,19 +3768,19 @@
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="3">
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{A83D83F3-3B26-4E37-A8DD-007161044665}">
           <x14:formula1>
-            <xm:f>その他!$B$3:$B$6</xm:f>
+            <xm:f>プルダウン用!$B$3:$B$6</xm:f>
           </x14:formula1>
           <xm:sqref>G126:G127 G129:G1048576 G1:G26 G28:G121</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{66D8840C-D443-486F-BC72-01200775D285}">
           <x14:formula1>
-            <xm:f>その他!$D$3:$D$6</xm:f>
+            <xm:f>プルダウン用!$D$3:$D$6</xm:f>
           </x14:formula1>
-          <xm:sqref>F126:F127 F129:F1048576 F1:F26 F28:F121</xm:sqref>
+          <xm:sqref>F1:F2 F129:F1048576 F127 F3:F126</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{D61B1C0A-2748-4606-B0EE-00EEC89A23C6}">
           <x14:formula1>
-            <xm:f>その他!$F$3:$F$6</xm:f>
+            <xm:f>プルダウン用!$F$3:$F$6</xm:f>
           </x14:formula1>
           <xm:sqref>E126:E127 E129:E1048576 E1:E26 E28:E121</xm:sqref>
         </x14:dataValidation>
@@ -4278,34 +3808,34 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:13" ht="19.5">
-      <c r="B2" s="39" t="s">
+      <c r="B2" s="37" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="39" t="s">
-        <v>122</v>
-      </c>
-      <c r="D2" s="50" t="s">
-        <v>103</v>
-      </c>
-      <c r="E2" s="50" t="s">
-        <v>140</v>
-      </c>
-      <c r="F2" s="50" t="s">
-        <v>141</v>
-      </c>
-      <c r="G2" s="37" t="s">
-        <v>66</v>
-      </c>
-      <c r="I2" s="30" t="s">
-        <v>20</v>
-      </c>
-      <c r="J2" s="29">
+      <c r="C2" s="37" t="s">
+        <v>97</v>
+      </c>
+      <c r="D2" s="48" t="s">
+        <v>82</v>
+      </c>
+      <c r="E2" s="48" t="s">
+        <v>112</v>
+      </c>
+      <c r="F2" s="48" t="s">
+        <v>113</v>
+      </c>
+      <c r="G2" s="35" t="s">
+        <v>47</v>
+      </c>
+      <c r="I2" s="28" t="s">
+        <v>16</v>
+      </c>
+      <c r="J2" s="27">
         <f>SUM(C:C)</f>
-        <v>181</v>
-      </c>
-      <c r="K2" s="29"/>
-      <c r="L2" s="28"/>
-      <c r="M2" s="28"/>
+        <v>160.5</v>
+      </c>
+      <c r="K2" s="27"/>
+      <c r="L2" s="26"/>
+      <c r="M2" s="26"/>
     </row>
     <row r="3" spans="2:13" ht="19.5">
       <c r="B3" s="18" t="s">
@@ -4313,560 +3843,479 @@
       </c>
       <c r="C3" s="19">
         <f>SUMIF(コスト表!B:B, B3, コスト表!D:D)</f>
-        <v>37.5</v>
-      </c>
-      <c r="D3" s="51">
+        <v>17</v>
+      </c>
+      <c r="D3" s="49">
         <f>SUMIFS(コスト表!D:D, コスト表!B:B, "プレイヤー", コスト表!G:G, "完了")</f>
-        <v>28</v>
-      </c>
-      <c r="E3" s="51">
+        <v>6.5</v>
+      </c>
+      <c r="E3" s="49">
         <f>SUMIFS(コスト表!D:D, コスト表!B:B, "プレイヤー", コスト表!G:G, "作業中")</f>
         <v>4</v>
       </c>
-      <c r="F3" s="51">
+      <c r="F3" s="49">
         <f>SUMIFS(コスト表!D:D, コスト表!B:B, "プレイヤー", コスト表!G:G, "未着手")</f>
-        <v>5.5</v>
-      </c>
-      <c r="G3" s="40">
+        <v>6.5</v>
+      </c>
+      <c r="G3" s="38">
         <f>ROUNDDOWN(COUNTIFS(コスト表!B:B, "プレイヤー", コスト表!G:G, "完了") / COUNTIF(コスト表!B:B, "プレイヤー") * 100,1)</f>
-        <v>75</v>
-      </c>
-      <c r="I3" s="31" t="s">
-        <v>21</v>
-      </c>
-      <c r="J3" s="29">
+        <v>33.299999999999997</v>
+      </c>
+      <c r="I3" s="29" t="s">
+        <v>17</v>
+      </c>
+      <c r="J3" s="27">
         <f>SUMIF(コスト表!G:G,"完了",コスト表!D:D)</f>
-        <v>110</v>
-      </c>
-      <c r="K3" s="28" t="s">
-        <v>22</v>
-      </c>
-      <c r="M3" s="28"/>
+        <v>88.5</v>
+      </c>
+      <c r="K3" s="26" t="s">
+        <v>18</v>
+      </c>
+      <c r="M3" s="26"/>
     </row>
     <row r="4" spans="2:13" ht="19.5">
       <c r="B4" s="1" t="s">
-        <v>138</v>
+        <v>111</v>
       </c>
       <c r="C4" s="19">
         <f>SUMIF(コスト表!B:B, B4, コスト表!D:D)</f>
         <v>27</v>
       </c>
-      <c r="D4" s="51">
+      <c r="D4" s="49">
         <f>SUMIFS(コスト表!D:D, コスト表!B:B, "敵ベース", コスト表!G:G, "完了")</f>
         <v>21</v>
       </c>
-      <c r="E4" s="51">
+      <c r="E4" s="49">
         <f>SUMIFS(コスト表!D:D, コスト表!B:B, "敵ベース", コスト表!G:G, "作業中")</f>
         <v>3</v>
       </c>
-      <c r="F4" s="51">
+      <c r="F4" s="49">
         <f>SUMIFS(コスト表!D:D, コスト表!B:B, "敵ベース", コスト表!G:G, "未着手")</f>
         <v>3</v>
       </c>
-      <c r="G4" s="40">
+      <c r="G4" s="38">
         <f>ROUNDDOWN(COUNTIFS(コスト表!B:B, "敵ベース", コスト表!G:G, "完了") / COUNTIF(コスト表!B:B, "敵ベース") * 100,1)</f>
         <v>71.400000000000006</v>
       </c>
-      <c r="I4" s="32" t="s">
-        <v>23</v>
-      </c>
-      <c r="J4" s="29">
+      <c r="I4" s="30" t="s">
+        <v>19</v>
+      </c>
+      <c r="J4" s="27">
         <f ca="1">NETWORKDAYS(J5,J6)</f>
-        <v>62</v>
-      </c>
-      <c r="K4" s="29">
+        <v>29</v>
+      </c>
+      <c r="K4" s="27">
         <f ca="1" xml:space="preserve"> ROUNDDOWN(J3 / J4,1)</f>
-        <v>1.7</v>
-      </c>
-      <c r="M4" s="28"/>
+        <v>3</v>
+      </c>
+      <c r="M4" s="26"/>
     </row>
     <row r="5" spans="2:13" ht="19.5">
       <c r="B5" s="18" t="s">
-        <v>40</v>
+        <v>24</v>
       </c>
       <c r="C5" s="19">
         <f>SUMIF(コスト表!B:B, B5, コスト表!D:D)</f>
         <v>10.5</v>
       </c>
-      <c r="D5" s="51">
+      <c r="D5" s="49">
         <f>SUMIFS(コスト表!D:D, コスト表!B:B, "敵1(通常ゾンビ)", コスト表!G:G, "完了")</f>
         <v>7.5</v>
       </c>
-      <c r="E5" s="51">
+      <c r="E5" s="49">
         <f>SUMIFS(コスト表!D:D, コスト表!B:B, "敵1(通常ゾンビ)", コスト表!G:G, "作業中")</f>
         <v>1</v>
       </c>
-      <c r="F5" s="51">
+      <c r="F5" s="49">
         <f>SUMIFS(コスト表!D:D, コスト表!B:B, "敵1(通常ゾンビ)", コスト表!G:G, "未着手")</f>
         <v>2</v>
       </c>
-      <c r="G5" s="40">
+      <c r="G5" s="38">
         <f>ROUNDDOWN(COUNTIFS(コスト表!B:B, "敵1(通常ゾンビ)", コスト表!G:G, "完了") / COUNTIF(コスト表!B:B, "敵1(通常ゾンビ)") * 100,1)</f>
         <v>66.599999999999994</v>
       </c>
-      <c r="I5" s="33" t="s">
-        <v>24</v>
-      </c>
-      <c r="J5" s="46">
-        <f>DATE(2025,5,2)</f>
-        <v>45779</v>
-      </c>
-      <c r="K5" s="46"/>
-      <c r="L5" s="28"/>
-      <c r="M5" s="28"/>
+      <c r="I5" s="31" t="s">
+        <v>20</v>
+      </c>
+      <c r="J5" s="44">
+        <f>DATE(2025,10,1)</f>
+        <v>45931</v>
+      </c>
+      <c r="K5" s="44"/>
+      <c r="L5" s="26"/>
+      <c r="M5" s="26"/>
     </row>
     <row r="6" spans="2:13" ht="19.5">
       <c r="B6" s="18" t="s">
-        <v>41</v>
+        <v>25</v>
       </c>
       <c r="C6" s="19">
         <f>SUMIF(コスト表!B:B, B6, コスト表!D:D)</f>
         <v>10.5</v>
       </c>
-      <c r="D6" s="51">
+      <c r="D6" s="49">
         <f>SUMIFS(コスト表!D:D, コスト表!B:B, "敵2(ランナーゾンビ)", コスト表!G:G, "完了")</f>
         <v>7.5</v>
       </c>
-      <c r="E6" s="51">
+      <c r="E6" s="49">
         <f>SUMIFS(コスト表!D:D, コスト表!B:B, "敵2(ランナーゾンビ)", コスト表!G:G, "作業中")</f>
         <v>1</v>
       </c>
-      <c r="F6" s="51">
+      <c r="F6" s="49">
         <f>SUMIFS(コスト表!D:D,コスト表!B:B,"敵2(ランナーゾンビ)",コスト表!G:G,"未着手")</f>
         <v>2</v>
       </c>
-      <c r="G6" s="40">
+      <c r="G6" s="38">
         <f>ROUNDDOWN(COUNTIFS(コスト表!B:B, "敵2(ランナーゾンビ)", コスト表!G:G, "完了") / COUNTIF(コスト表!B:B, "敵2(ランナーゾンビ)") * 100,1)</f>
         <v>66.599999999999994</v>
       </c>
-      <c r="I6" s="34" t="s">
-        <v>25</v>
-      </c>
-      <c r="J6" s="46">
+      <c r="I6" s="32" t="s">
+        <v>21</v>
+      </c>
+      <c r="J6" s="44">
         <f ca="1">TODAY()</f>
-        <v>45866</v>
-      </c>
-      <c r="K6" s="46"/>
-      <c r="L6" s="28"/>
-      <c r="M6" s="28"/>
+        <v>45971</v>
+      </c>
+      <c r="K6" s="44"/>
+      <c r="L6" s="26"/>
+      <c r="M6" s="26"/>
     </row>
     <row r="7" spans="2:13">
       <c r="B7" s="18" t="s">
-        <v>82</v>
+        <v>63</v>
       </c>
       <c r="C7" s="19">
         <f>SUMIF(コスト表!B:B, B7, コスト表!D:D)</f>
         <v>10.5</v>
       </c>
-      <c r="D7" s="51">
+      <c r="D7" s="49">
         <f>SUMIFS(コスト表!D:D, コスト表!B:B, "敵3(遠距離型ゾンビ)", コスト表!G:G, "完了")</f>
         <v>7.5</v>
       </c>
-      <c r="E7" s="51">
+      <c r="E7" s="49">
         <f>SUMIFS(コスト表!D:D, コスト表!B:B, "敵3(遠距離型ゾンビ)", コスト表!G:G, "作業中")</f>
         <v>1</v>
       </c>
-      <c r="F7" s="51">
+      <c r="F7" s="49">
         <f>SUMIFS(コスト表!D:D, コスト表!B:B, "敵3(遠距離型ゾンビ)", コスト表!G:G, "未着手")</f>
         <v>2</v>
       </c>
-      <c r="G7" s="40">
+      <c r="G7" s="38">
         <f>ROUNDDOWN(COUNTIFS(コスト表!B:B, "敵3(遠距離型ゾンビ)", コスト表!G:G, "完了") / COUNTIF(コスト表!B:B, "敵3(遠距離型ゾンビ)") * 100,1)</f>
         <v>66.599999999999994</v>
       </c>
-      <c r="M7" s="28"/>
+      <c r="M7" s="26"/>
     </row>
     <row r="8" spans="2:13">
       <c r="B8" s="18" t="s">
-        <v>72</v>
+        <v>53</v>
       </c>
       <c r="C8" s="19">
         <f>SUMIF(コスト表!B:B, B8, コスト表!D:D)</f>
         <v>24</v>
       </c>
-      <c r="D8" s="51">
+      <c r="D8" s="49">
         <f>SUMIFS(コスト表!D:D, コスト表!B:B, "ボス(ゾンビを召喚)", コスト表!G:G, "完了")</f>
         <v>0</v>
       </c>
-      <c r="E8" s="51">
+      <c r="E8" s="49">
         <f>SUMIFS(コスト表!D:D, コスト表!B:B, "ボス(ゾンビを召喚)", コスト表!G:G, "作業中")</f>
         <v>0</v>
       </c>
-      <c r="F8" s="51">
+      <c r="F8" s="49">
         <f>SUMIFS(コスト表!D:D,コスト表!B:B,"ボス(ゾンビを召喚)",コスト表!G:G,"未着手")</f>
         <v>24</v>
       </c>
-      <c r="G8" s="40">
+      <c r="G8" s="38">
         <f>ROUNDDOWN(COUNTIFS(コスト表!B:B, "ボス(ゾンビを召喚)", コスト表!G:G, "完了") / COUNTIF(コスト表!B:B, "ボス(ゾンビを召喚)") * 100,1)</f>
         <v>0</v>
       </c>
-      <c r="I8" s="28"/>
-      <c r="J8" s="28"/>
-      <c r="K8" s="28" t="s">
-        <v>26</v>
-      </c>
-      <c r="L8" s="28" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="9" spans="2:13" ht="24">
+      <c r="I8" s="40" t="s">
+        <v>4</v>
+      </c>
+      <c r="J8" s="40" t="s">
+        <v>49</v>
+      </c>
+      <c r="K8" s="40" t="s">
+        <v>82</v>
+      </c>
+      <c r="L8" s="40" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="9" spans="2:13">
       <c r="B9" s="1" t="s">
-        <v>119</v>
+        <v>94</v>
       </c>
       <c r="C9" s="19">
         <f>SUMIF(コスト表!B:B, B9, コスト表!D:D)</f>
         <v>8</v>
       </c>
-      <c r="D9" s="51">
+      <c r="D9" s="49">
         <f>SUMIFS(コスト表!D:D, コスト表!B:B, "マップ", コスト表!G:G, "完了")</f>
         <v>8</v>
       </c>
-      <c r="E9" s="51">
+      <c r="E9" s="49">
         <f>SUMIFS(コスト表!D:D, コスト表!B:B, "マップ", コスト表!G:G, "作業中")</f>
         <v>0</v>
       </c>
-      <c r="F9" s="51">
+      <c r="F9" s="49">
         <f>SUMIFS(コスト表!D:D, コスト表!B:B, "マップ", コスト表!G:G, "未着手")</f>
         <v>0</v>
       </c>
-      <c r="G9" s="40">
+      <c r="G9" s="38">
         <f>ROUNDDOWN(COUNTIFS(コスト表!B:B, "マップ", コスト表!G:G, "完了") / COUNTIF(コスト表!B:B, "マップ") * 100,1)</f>
         <v>100</v>
       </c>
-      <c r="I9" s="55" t="s">
-        <v>65</v>
-      </c>
-      <c r="J9" s="61">
-        <f>DATE(2025,7,23)</f>
-        <v>45861</v>
-      </c>
-      <c r="K9" s="57">
-        <f ca="1">NETWORKDAYS(TODAY(),J9)</f>
-        <v>-4</v>
-      </c>
-      <c r="L9" s="59">
-        <f ca="1">ROUNDDOWN(($J$2-$J$3)/K9, 1)</f>
-        <v>-17.7</v>
-      </c>
-    </row>
-    <row r="10" spans="2:13" ht="19.5">
+      <c r="I9" s="19" t="s">
+        <v>130</v>
+      </c>
+      <c r="J9" s="18"/>
+      <c r="K9" s="18"/>
+      <c r="L9" s="18"/>
+    </row>
+    <row r="10" spans="2:13">
       <c r="B10" s="18" t="s">
-        <v>123</v>
+        <v>98</v>
       </c>
       <c r="C10" s="19">
         <f>SUMIF(コスト表!B:B, B10, コスト表!D:D)</f>
         <v>27</v>
       </c>
-      <c r="D10" s="51">
+      <c r="D10" s="49">
         <f>SUMIFS(コスト表!D:D, コスト表!B:B, "ウェーブ管理", コスト表!G:G, "完了")</f>
         <v>16</v>
       </c>
-      <c r="E10" s="51">
+      <c r="E10" s="49">
         <f>SUMIFS(コスト表!D:D, コスト表!B:B, "ウェーブ管理", コスト表!G:G, "作業中")</f>
         <v>3</v>
       </c>
-      <c r="F10" s="51">
+      <c r="F10" s="49">
         <f>SUMIFS(コスト表!D:D, コスト表!B:B, "ウェーブ管理", コスト表!G:G, "未着手")</f>
         <v>8</v>
       </c>
-      <c r="G10" s="40">
+      <c r="G10" s="38">
         <f>ROUNDDOWN(COUNTIFS(コスト表!B:B, "ウェーブ管理", コスト表!G:G, "完了") / COUNTIF(コスト表!B:B, "ウェーブ管理") * 100,1)</f>
         <v>62.5</v>
       </c>
-      <c r="I10" s="30" t="s">
-        <v>28</v>
-      </c>
-      <c r="J10" s="62">
-        <f>DATE(2025,8,7)</f>
-        <v>45876</v>
-      </c>
-      <c r="K10" s="58">
-        <f ca="1">NETWORKDAYS(TODAY(),J10)</f>
-        <v>9</v>
-      </c>
-      <c r="L10" s="60">
-        <f ca="1">ROUNDDOWN(($J$2 - $J$3) / K10,1)</f>
-        <v>7.8</v>
-      </c>
-    </row>
-    <row r="11" spans="2:13" ht="19.5">
+      <c r="I10" s="41" t="s">
+        <v>126</v>
+      </c>
+      <c r="J10" s="41">
+        <f>SUMIF(コスト表!F:F, "プロト", コスト表!D:D)</f>
+        <v>0</v>
+      </c>
+      <c r="K10" s="41">
+        <f>SUMIFS(コスト表!D:D, コスト表!F:F, "プロト", コスト表!G:G, "完了")</f>
+        <v>0</v>
+      </c>
+      <c r="L10" s="41" t="e">
+        <f>ROUNDDOWN(COUNTIFS(コスト表!F:F, "プロト", コスト表!G:G, "完了") / COUNTIF(コスト表!F:F, "プロト") * 100,1)</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="11" spans="2:13">
       <c r="B11" s="18" t="s">
-        <v>52</v>
+        <v>36</v>
       </c>
       <c r="C11" s="19">
         <f>SUMIF(コスト表!B:B, B11, コスト表!D:D)</f>
         <v>8.5</v>
       </c>
-      <c r="D11" s="51">
+      <c r="D11" s="49">
         <f>SUMIFS(コスト表!D:D, コスト表!B:B, "アイテム", コスト表!G:G, "完了")</f>
         <v>8.5</v>
       </c>
-      <c r="E11" s="51">
+      <c r="E11" s="49">
         <f>SUMIFS(コスト表!D:D, コスト表!B:B, "アイテム", コスト表!G:G, "作業中")</f>
         <v>0</v>
       </c>
-      <c r="F11" s="51">
+      <c r="F11" s="49">
         <f>SUMIFS(コスト表!D:D, コスト表!B:B, "アイテム", コスト表!G:G, "未着手")</f>
         <v>0</v>
       </c>
-      <c r="G11" s="40">
+      <c r="G11" s="38">
         <f>ROUNDDOWN(COUNTIFS(コスト表!B:B, "アイテム", コスト表!G:G, "完了") / COUNTIF(コスト表!B:B, "アイテム") * 100,1)</f>
         <v>100</v>
       </c>
-      <c r="I11" s="31" t="s">
-        <v>29</v>
-      </c>
-      <c r="J11" s="62">
-        <f>DATE(2025,8,14)</f>
-        <v>45883</v>
-      </c>
-      <c r="K11" s="58">
-        <f ca="1">NETWORKDAYS(TODAY(),J11)</f>
-        <v>14</v>
-      </c>
-      <c r="L11" s="60">
-        <f ca="1">ROUNDDOWN(($J$2 - $J$3) / K11,1)</f>
-        <v>5</v>
-      </c>
-    </row>
-    <row r="12" spans="2:13" ht="19.5">
+      <c r="I11" s="41" t="s">
+        <v>127</v>
+      </c>
+      <c r="J11" s="41">
+        <f>SUMIF(コスト表!F:F, "アルファ", コスト表!D:D)</f>
+        <v>0</v>
+      </c>
+      <c r="K11" s="41">
+        <f>SUMIFS(コスト表!D:D, コスト表!F:F, "アルファ", コスト表!G:G, "完了")</f>
+        <v>0</v>
+      </c>
+      <c r="L11" s="41" t="e">
+        <f>ROUNDDOWN(COUNTIFS(コスト表!F:F, "アルファ", コスト表!G:G, "完了") / COUNTIF(コスト表!F:F, "アルファ") * 100,1)</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="12" spans="2:13">
       <c r="B12" s="18" t="s">
-        <v>55</v>
+        <v>38</v>
       </c>
       <c r="C12" s="19">
         <f>SUMIF(コスト表!B:B, B12, コスト表!D:D)</f>
         <v>4</v>
       </c>
-      <c r="D12" s="51">
+      <c r="D12" s="49">
         <f>SUMIFS(コスト表!D:D, コスト表!B:B, "タイトル", コスト表!G:G, "完了")</f>
         <v>2</v>
       </c>
-      <c r="E12" s="51">
+      <c r="E12" s="49">
         <f>SUMIFS(コスト表!D:D, コスト表!B:B, "タイトル", コスト表!G:G, "作業中")</f>
         <v>0</v>
       </c>
-      <c r="F12" s="51">
+      <c r="F12" s="49">
         <f>SUMIFS(コスト表!D:D, コスト表!B:B, "タイトル", コスト表!G:G, "未着手")</f>
         <v>2</v>
       </c>
-      <c r="G12" s="40">
+      <c r="G12" s="38">
         <f>ROUNDDOWN(COUNTIFS(コスト表!B:B, "タイトル", コスト表!G:G, "完了") / COUNTIF(コスト表!B:B, "タイトル") * 100,1)</f>
         <v>60</v>
       </c>
-      <c r="I12" s="56" t="s">
-        <v>30</v>
-      </c>
-      <c r="J12" s="62">
-        <f>DATE(2025,9,1)</f>
-        <v>45901</v>
-      </c>
-      <c r="K12" s="58">
-        <f ca="1">NETWORKDAYS(TODAY(),J12)</f>
-        <v>26</v>
-      </c>
-      <c r="L12" s="60">
-        <f ca="1">ROUNDDOWN(($J$2 - $J$3) / K12,1)</f>
-        <v>2.7</v>
+      <c r="I12" s="41" t="s">
+        <v>128</v>
+      </c>
+      <c r="J12" s="41">
+        <f>SUMIF(コスト表!F:F, "ベータ", コスト表!D:D)</f>
+        <v>0</v>
+      </c>
+      <c r="K12" s="41">
+        <f>SUMIFS(コスト表!D:D, コスト表!F:F, "ベータ", コスト表!G:G, "完了")</f>
+        <v>0</v>
+      </c>
+      <c r="L12" s="41" t="e">
+        <f>ROUNDDOWN(COUNTIFS(コスト表!F:F, "ベータ", コスト表!G:G, "完了") / COUNTIF(コスト表!F:F, "ベータ") * 100,1)</f>
+        <v>#DIV/0!</v>
       </c>
     </row>
     <row r="13" spans="2:13">
       <c r="B13" s="18" t="s">
-        <v>130</v>
+        <v>103</v>
       </c>
       <c r="C13" s="19">
         <f>SUMIF(コスト表!B:B, B13, コスト表!D:D)</f>
         <v>4</v>
       </c>
-      <c r="D13" s="51">
+      <c r="D13" s="49">
         <f>SUMIFS(コスト表!D:D, コスト表!B:B, "リザルト", コスト表!G:G, "完了")</f>
         <v>2</v>
       </c>
-      <c r="E13" s="51">
+      <c r="E13" s="49">
         <f>SUMIFS(コスト表!D:D, コスト表!B:B, "リザルト", コスト表!G:G, "作業中")</f>
         <v>0</v>
       </c>
-      <c r="F13" s="51">
+      <c r="F13" s="49">
         <f>SUMIFS(コスト表!D:D, コスト表!B:B, "リザルト", コスト表!G:G, "未着手")</f>
         <v>2</v>
       </c>
-      <c r="G13" s="40">
+      <c r="G13" s="38">
         <f>ROUNDDOWN(COUNTIFS(コスト表!B:B, "リザルト", コスト表!G:G, "完了") / COUNTIF(コスト表!B:B, "リザルト") * 100,1)</f>
         <v>60</v>
       </c>
-      <c r="J13" s="46"/>
-      <c r="K13" s="44"/>
-      <c r="L13" s="29"/>
+      <c r="J13" s="44"/>
+      <c r="K13" s="42"/>
+      <c r="L13" s="27"/>
     </row>
     <row r="14" spans="2:13">
       <c r="B14" s="18" t="s">
-        <v>59</v>
+        <v>42</v>
       </c>
       <c r="C14" s="19">
         <f>SUMIF(コスト表!B:B, B14, コスト表!D:D)</f>
         <v>6.5</v>
       </c>
-      <c r="D14" s="51">
+      <c r="D14" s="49">
         <f>SUMIFS(コスト表!D:D, コスト表!B:B, "オプション", コスト表!G:G, "完了")</f>
         <v>0</v>
       </c>
-      <c r="E14" s="51">
+      <c r="E14" s="49">
         <f>SUMIFS(コスト表!D:D, コスト表!B:B, "オプション", コスト表!G:G, "作業中")</f>
         <v>0</v>
       </c>
-      <c r="F14" s="51">
+      <c r="F14" s="49">
         <f>SUMIFS(コスト表!D:D,コスト表!B:B,"オプション",コスト表!G:G,"未着手")</f>
         <v>6.5</v>
       </c>
-      <c r="G14" s="40">
+      <c r="G14" s="38">
         <f>ROUNDDOWN(COUNTIFS(コスト表!B:B, "オプション", コスト表!G:G, "完了") / COUNTIF(コスト表!B:B, "オプション") * 100,1)</f>
         <v>0</v>
       </c>
-      <c r="I14" s="42" t="s">
-        <v>4</v>
-      </c>
-      <c r="J14" s="42" t="s">
-        <v>68</v>
-      </c>
-      <c r="K14" s="42" t="s">
-        <v>103</v>
-      </c>
-      <c r="L14" s="42" t="s">
-        <v>69</v>
-      </c>
     </row>
     <row r="15" spans="2:13">
-      <c r="B15" s="41" t="s">
-        <v>147</v>
-      </c>
-      <c r="C15" s="66">
+      <c r="B15" s="39" t="s">
+        <v>119</v>
+      </c>
+      <c r="C15" s="56">
         <f>SUMIF(コスト表!B:B, B15, コスト表!D:D)</f>
         <v>3</v>
       </c>
-      <c r="D15" s="66">
+      <c r="D15" s="56">
         <f>SUMIFS(コスト表!D:D, コスト表!B:B, "ゲームオーバー", コスト表!G:G, "完了")</f>
         <v>2</v>
       </c>
-      <c r="E15" s="66">
+      <c r="E15" s="56">
         <f>SUMIFS(コスト表!D:D, コスト表!B:B, "ゲームオーバー", コスト表!G:G, "作業中")</f>
         <v>0</v>
       </c>
-      <c r="F15" s="66">
+      <c r="F15" s="56">
         <f>SUMIFS(コスト表!D:D, コスト表!B:B, "ゲームオーバー", コスト表!G:G, "未着手")</f>
         <v>1</v>
       </c>
-      <c r="G15" s="43">
+      <c r="G15" s="41">
         <f>ROUNDDOWN(COUNTIFS(コスト表!B:B, "ゲームオーバー", コスト表!G:G, "完了") / COUNTIF(コスト表!B:B, "ゲームオーバー") * 100,1)</f>
         <v>75</v>
       </c>
-      <c r="I15" s="43" t="s">
-        <v>9</v>
-      </c>
-      <c r="J15" s="43">
-        <f>SUMIF(コスト表!F:F, "プロト", コスト表!D:D)</f>
-        <v>125.5</v>
-      </c>
-      <c r="K15" s="43">
-        <f>SUMIFS(コスト表!D:D, コスト表!F:F, "プロト", コスト表!G:G, "完了")</f>
-        <v>89</v>
-      </c>
-      <c r="L15" s="43">
-        <f>ROUNDDOWN(COUNTIFS(コスト表!F:F, "プロト", コスト表!G:G, "完了") / COUNTIF(コスト表!F:F, "プロト") * 100,1)</f>
-        <v>72.8</v>
-      </c>
     </row>
     <row r="16" spans="2:13">
-      <c r="B16" s="41" t="s">
-        <v>67</v>
+      <c r="B16" s="39" t="s">
+        <v>48</v>
       </c>
       <c r="C16" s="9"/>
       <c r="D16" s="9"/>
       <c r="E16" s="9"/>
       <c r="F16" s="9"/>
-      <c r="G16" s="40">
+      <c r="G16" s="38">
         <f>ROUNDDOWN(COUNTIF(コスト表!G:G, "完了") / COUNTA(コスト表!G:G) * 100,1)</f>
-        <v>61</v>
-      </c>
-      <c r="I16" s="43" t="s">
-        <v>12</v>
-      </c>
-      <c r="J16" s="43">
-        <f>SUMIF(コスト表!F:F, "アルファ", コスト表!D:D)</f>
-        <v>52.5</v>
-      </c>
-      <c r="K16" s="43">
-        <f>SUMIFS(コスト表!D:D, コスト表!F:F, "アルファ", コスト表!G:G, "完了")</f>
-        <v>20</v>
-      </c>
-      <c r="L16" s="43">
-        <f>ROUNDDOWN(COUNTIFS(コスト表!F:F, "アルファ", コスト表!G:G, "完了") / COUNTIF(コスト表!F:F, "アルファ") * 100,1)</f>
-        <v>42.4</v>
-      </c>
-    </row>
-    <row r="17" spans="3:12">
-      <c r="I17" s="43" t="s">
-        <v>17</v>
-      </c>
-      <c r="J17" s="43">
-        <f>SUMIF(コスト表!F:F, "ベータ", コスト表!D:D)</f>
-        <v>3</v>
-      </c>
-      <c r="K17" s="43">
-        <f>SUMIFS(コスト表!D:D, コスト表!F:F, "ベータ", コスト表!G:G, "完了")</f>
-        <v>1</v>
-      </c>
-      <c r="L17" s="43">
-        <f>ROUNDDOWN(COUNTIFS(コスト表!F:F, "ベータ", コスト表!G:G, "完了") / COUNTIF(コスト表!F:F, "ベータ") * 100,1)</f>
-        <v>50</v>
-      </c>
-    </row>
-    <row r="18" spans="3:12">
-      <c r="I18" s="43" t="s">
-        <v>18</v>
-      </c>
-      <c r="J18" s="43">
-        <f>SUMIF(コスト表!F:F, "マスター", コスト表!D:D)</f>
-        <v>0</v>
-      </c>
-      <c r="K18" s="43">
-        <f>SUMIFS(コスト表!D:D, コスト表!F:F, "マスター", コスト表!G:G, "完了")</f>
-        <v>0</v>
-      </c>
-      <c r="L18" s="43" t="e">
-        <f>ROUNDDOWN(COUNTIFS(コスト表!F:F, "マスター", コスト表!G:G, "完了") / COUNTIF(コスト表!F:F, "マスター") * 100,1)</f>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="19" spans="3:12">
+        <v>56.4</v>
+      </c>
+    </row>
+    <row r="19" spans="3:7">
       <c r="C19" s="7"/>
       <c r="D19" s="7"/>
       <c r="E19" s="7"/>
       <c r="F19" s="7"/>
-      <c r="G19" s="38"/>
-    </row>
-    <row r="20" spans="3:12">
+      <c r="G19" s="36"/>
+    </row>
+    <row r="20" spans="3:7">
       <c r="C20" s="7"/>
       <c r="D20" s="7"/>
       <c r="E20" s="7"/>
       <c r="F20" s="7"/>
-      <c r="G20" s="38"/>
-    </row>
-    <row r="21" spans="3:12">
-      <c r="G21" s="38"/>
-    </row>
-    <row r="22" spans="3:12">
-      <c r="G22" s="38"/>
-    </row>
-    <row r="24" spans="3:12">
-      <c r="G24" s="36"/>
-    </row>
-    <row r="25" spans="3:12">
-      <c r="G25" s="36"/>
-    </row>
-    <row r="26" spans="3:12">
-      <c r="G26" s="36"/>
-    </row>
-    <row r="27" spans="3:12">
-      <c r="G27" s="36"/>
+      <c r="G20" s="36"/>
+    </row>
+    <row r="21" spans="3:7">
+      <c r="G21" s="36"/>
+    </row>
+    <row r="22" spans="3:7">
+      <c r="G22" s="36"/>
+    </row>
+    <row r="24" spans="3:7">
+      <c r="G24" s="34"/>
+    </row>
+    <row r="25" spans="3:7">
+      <c r="G25" s="34"/>
+    </row>
+    <row r="26" spans="3:7">
+      <c r="G26" s="34"/>
+    </row>
+    <row r="27" spans="3:7">
+      <c r="G27" s="34"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1"/>
@@ -4885,86 +4334,83 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:6">
-      <c r="B2" s="35" t="s">
-        <v>16</v>
-      </c>
-      <c r="D2" s="35" t="s">
+      <c r="B2" s="33" t="s">
+        <v>14</v>
+      </c>
+      <c r="D2" s="33" t="s">
         <v>4</v>
       </c>
-      <c r="F2" s="35" t="s">
+      <c r="F2" s="33" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="3" spans="2:6">
       <c r="B3" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="D3" s="20" t="s">
+        <v>130</v>
+      </c>
+      <c r="F3" s="20" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4" spans="2:6">
+      <c r="B4" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="D4" s="20" t="s">
+        <v>126</v>
+      </c>
+      <c r="F4" s="20" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="5" spans="2:6">
+      <c r="B5" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="D5" s="20" t="s">
+        <v>127</v>
+      </c>
+      <c r="F5" s="20" t="s">
         <v>10</v>
       </c>
-      <c r="D3" s="20" t="s">
-        <v>9</v>
-      </c>
-      <c r="F3" s="22" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="4" spans="2:6">
-      <c r="B4" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="D4" s="20" t="s">
-        <v>12</v>
-      </c>
-      <c r="F4" s="22" t="s">
+    </row>
+    <row r="6" spans="2:6">
+      <c r="B6" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="D6" s="21" t="s">
+        <v>128</v>
+      </c>
+      <c r="F6" s="21" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="5" spans="2:6">
-      <c r="B5" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="D5" s="20" t="s">
-        <v>17</v>
-      </c>
-      <c r="F5" s="22" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="6" spans="2:6">
-      <c r="B6" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="D6" s="21" t="s">
-        <v>18</v>
-      </c>
-      <c r="F6" s="23" t="s">
-        <v>19</v>
-      </c>
-    </row>
     <row r="8" spans="2:6">
-      <c r="B8" s="65" t="s">
+      <c r="B8" s="55" t="s">
         <v>3</v>
       </c>
-      <c r="D8" t="s">
-        <v>148</v>
-      </c>
     </row>
     <row r="9" spans="2:6">
-      <c r="B9" s="63" t="s">
-        <v>134</v>
+      <c r="B9" s="53" t="s">
+        <v>107</v>
       </c>
     </row>
     <row r="10" spans="2:6">
-      <c r="B10" s="63" t="s">
-        <v>135</v>
+      <c r="B10" s="53" t="s">
+        <v>108</v>
       </c>
     </row>
     <row r="11" spans="2:6">
-      <c r="B11" s="63" t="s">
-        <v>136</v>
+      <c r="B11" s="53" t="s">
+        <v>109</v>
       </c>
     </row>
     <row r="12" spans="2:6">
-      <c r="B12" s="64" t="s">
-        <v>137</v>
+      <c r="B12" s="54" t="s">
+        <v>110</v>
       </c>
     </row>
   </sheetData>
@@ -4974,21 +4420,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="ドキュメント" ma:contentTypeID="0x0101006836AD0B55474E4CAD520F1DEB8FB579" ma:contentTypeVersion="3" ma:contentTypeDescription="新しいドキュメントを作成します。" ma:contentTypeScope="" ma:versionID="078ba6c1f7b5b638bb57eb024ae572f7">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="187a6309-4c0c-49e3-bd2d-e8130eb88270" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="c5f182963113af090d1b42042cf04cb6" ns2:_="">
     <xsd:import namespace="187a6309-4c0c-49e3-bd2d-e8130eb88270"/>
@@ -5126,24 +4557,22 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BC0DB335-AD01-472D-90D0-5B4B126AC491}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E90E09EE-5F6D-4AB8-AE54-C74368FE6F4B}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5A1D85CE-B20E-4841-A55B-779E85453EF9}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -5159,4 +4588,21 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E90E09EE-5F6D-4AB8-AE54-C74368FE6F4B}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BC0DB335-AD01-472D-90D0-5B4B126AC491}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/ゾンビシューターゲームコスト表.xlsx
+++ b/ゾンビシューターゲームコスト表.xlsx
@@ -1,25 +1,25 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\由留部 瑛人.FICPCROOMB14\Documents\GitHub\MyGame3D2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{13F0E57A-DBD4-4D52-9BA3-401A4B37EB09}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FFD95B4E-9C1D-4106-875A-B989E12871D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3720" yWindow="2520" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2220" yWindow="3345" windowWidth="24600" windowHeight="11025" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="コスト表" sheetId="1" r:id="rId1"/>
-    <sheet name="分類別コスト集計" sheetId="2" r:id="rId2"/>
+    <sheet name="集計" sheetId="2" r:id="rId2"/>
     <sheet name="プルダウン用" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">コスト表!$E$2:$G$132</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">分類別コスト集計!$B$2:$G$21</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">コスト表!$E$2:$G$122</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">集計!$B$2:$G$21</definedName>
   </definedNames>
   <calcPr calcId="191028"/>
   <extLst>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="433" uniqueCount="137">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="423" uniqueCount="137">
   <si>
     <t>分類</t>
   </si>
@@ -1748,7 +1748,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B1:I132"/>
+  <dimension ref="B1:I122"/>
   <sheetFormatPr defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col min="2" max="2" width="27.5" bestFit="1" customWidth="1"/>
@@ -1848,7 +1848,7 @@
         <v>130</v>
       </c>
       <c r="G5" s="11" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H5" s="15"/>
     </row>
@@ -1890,7 +1890,7 @@
         <v>126</v>
       </c>
       <c r="G7" s="11" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
     </row>
     <row r="8" spans="2:8" ht="18.75">
@@ -1910,7 +1910,7 @@
         <v>126</v>
       </c>
       <c r="G8" s="11" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="H8" s="15"/>
     </row>
@@ -1952,7 +1952,7 @@
         <v>127</v>
       </c>
       <c r="G10" s="11" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="H10" s="15"/>
     </row>
@@ -2023,208 +2023,284 @@
       <c r="B14" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C14" s="1"/>
-      <c r="D14" s="7"/>
-      <c r="E14" s="5"/>
+      <c r="C14" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="D14" s="7">
+        <v>0.5</v>
+      </c>
+      <c r="E14" s="5" t="s">
+        <v>8</v>
+      </c>
       <c r="F14" s="11"/>
-      <c r="G14" s="11"/>
+      <c r="G14" s="11" t="s">
+        <v>12</v>
+      </c>
       <c r="H14" s="15"/>
     </row>
     <row r="15" spans="2:8" ht="18.75">
       <c r="B15" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="C15" s="1"/>
-      <c r="D15" s="7"/>
-      <c r="E15" s="5"/>
+        <v>7</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D15" s="7">
+        <v>0.5</v>
+      </c>
+      <c r="E15" s="5" t="s">
+        <v>8</v>
+      </c>
       <c r="F15" s="11"/>
-      <c r="G15" s="11"/>
+      <c r="G15" s="11" t="s">
+        <v>12</v>
+      </c>
       <c r="H15" s="15"/>
     </row>
     <row r="16" spans="2:8" ht="18.75">
       <c r="B16" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="C16" s="1"/>
-      <c r="D16" s="7"/>
-      <c r="E16" s="5"/>
+        <v>7</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="D16" s="7">
+        <v>0.5</v>
+      </c>
+      <c r="E16" s="5" t="s">
+        <v>8</v>
+      </c>
       <c r="F16" s="11"/>
-      <c r="G16" s="11"/>
+      <c r="G16" s="11" t="s">
+        <v>12</v>
+      </c>
       <c r="H16" s="15"/>
     </row>
     <row r="17" spans="2:8" ht="18.75">
-      <c r="B17" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="C17" s="1"/>
-      <c r="D17" s="7"/>
-      <c r="E17" s="5"/>
-      <c r="F17" s="11"/>
-      <c r="G17" s="11"/>
-      <c r="H17" s="15"/>
+      <c r="B17" s="39"/>
+      <c r="C17" s="45"/>
+      <c r="D17" s="46"/>
+      <c r="E17" s="45"/>
+      <c r="F17" s="45"/>
+      <c r="G17" s="45"/>
+      <c r="H17" s="6"/>
     </row>
     <row r="18" spans="2:8" ht="18.75">
-      <c r="B18" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C18" s="1"/>
-      <c r="D18" s="7"/>
-      <c r="E18" s="5"/>
-      <c r="F18" s="11"/>
-      <c r="G18" s="11"/>
-      <c r="H18" s="15"/>
+      <c r="B18" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="D18" s="8">
+        <v>5</v>
+      </c>
+      <c r="E18" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F18" s="10"/>
+      <c r="G18" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="H18" s="14" t="s">
+        <v>65</v>
+      </c>
     </row>
     <row r="19" spans="2:8" ht="18.75">
       <c r="B19" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C19" s="1"/>
-      <c r="D19" s="7"/>
-      <c r="E19" s="5"/>
+        <v>111</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="D19" s="7">
+        <v>4</v>
+      </c>
+      <c r="E19" s="5" t="s">
+        <v>8</v>
+      </c>
       <c r="F19" s="11"/>
-      <c r="G19" s="11"/>
-      <c r="H19" s="15"/>
+      <c r="G19" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="H19" s="15" t="s">
+        <v>122</v>
+      </c>
     </row>
     <row r="20" spans="2:8" ht="18.75">
       <c r="B20" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C20" s="1"/>
-      <c r="D20" s="7"/>
-      <c r="E20" s="5"/>
+        <v>111</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="D20" s="7">
+        <v>6</v>
+      </c>
+      <c r="E20" s="5" t="s">
+        <v>8</v>
+      </c>
       <c r="F20" s="11"/>
-      <c r="G20" s="11"/>
-      <c r="H20" s="15"/>
+      <c r="G20" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="H20" s="15" t="s">
+        <v>123</v>
+      </c>
     </row>
     <row r="21" spans="2:8" ht="18.75">
       <c r="B21" s="1" t="s">
-        <v>7</v>
+        <v>111</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>120</v>
+        <v>69</v>
       </c>
       <c r="D21" s="7">
-        <v>0.5</v>
+        <v>2</v>
       </c>
       <c r="E21" s="5" t="s">
         <v>8</v>
       </c>
       <c r="F21" s="11"/>
       <c r="G21" s="11" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="H21" s="15"/>
     </row>
     <row r="22" spans="2:8" ht="18.75">
       <c r="B22" s="1" t="s">
-        <v>7</v>
+        <v>111</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>23</v>
+        <v>70</v>
       </c>
       <c r="D22" s="7">
-        <v>0.5</v>
+        <v>4</v>
       </c>
       <c r="E22" s="5" t="s">
         <v>8</v>
       </c>
       <c r="F22" s="11"/>
       <c r="G22" s="11" t="s">
-        <v>9</v>
-      </c>
-      <c r="H22" s="15"/>
+        <v>12</v>
+      </c>
+      <c r="H22" s="15" t="s">
+        <v>71</v>
+      </c>
     </row>
     <row r="23" spans="2:8" ht="18.75">
       <c r="B23" s="1" t="s">
-        <v>7</v>
+        <v>111</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>26</v>
+        <v>72</v>
       </c>
       <c r="D23" s="7">
-        <v>0.5</v>
+        <v>3</v>
       </c>
       <c r="E23" s="5" t="s">
         <v>8</v>
       </c>
       <c r="F23" s="11"/>
       <c r="G23" s="11" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H23" s="15"/>
     </row>
     <row r="24" spans="2:8" ht="18.75">
       <c r="B24" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="C24" s="1"/>
-      <c r="D24" s="7"/>
-      <c r="E24" s="5"/>
+        <v>111</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="D24" s="7">
+        <v>3</v>
+      </c>
+      <c r="E24" s="5" t="s">
+        <v>8</v>
+      </c>
       <c r="F24" s="11"/>
-      <c r="G24" s="11"/>
+      <c r="G24" s="11" t="s">
+        <v>11</v>
+      </c>
       <c r="H24" s="15"/>
     </row>
     <row r="25" spans="2:8" ht="18.75">
-      <c r="B25" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="C25" s="1"/>
+      <c r="B25" s="2"/>
+      <c r="C25" s="2"/>
       <c r="D25" s="7"/>
-      <c r="E25" s="5"/>
-      <c r="F25" s="11"/>
-      <c r="G25" s="11"/>
-      <c r="H25" s="47"/>
+      <c r="E25" s="6"/>
+      <c r="F25" s="12"/>
+      <c r="G25" s="12"/>
+      <c r="H25" s="16"/>
     </row>
     <row r="26" spans="2:8" ht="18.75">
       <c r="B26" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C26" s="1"/>
-      <c r="D26" s="7"/>
-      <c r="E26" s="5"/>
+        <v>24</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="D26" s="4">
+        <v>1.5</v>
+      </c>
+      <c r="E26" s="5" t="s">
+        <v>8</v>
+      </c>
       <c r="F26" s="11"/>
-      <c r="G26" s="11"/>
-      <c r="H26" s="5"/>
+      <c r="G26" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="H26" s="15"/>
     </row>
     <row r="27" spans="2:8" ht="18.75">
-      <c r="B27" s="39"/>
-      <c r="C27" s="45"/>
-      <c r="D27" s="46"/>
-      <c r="E27" s="45"/>
-      <c r="F27" s="45"/>
-      <c r="G27" s="45"/>
-      <c r="H27" s="6"/>
+      <c r="B27" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="D27" s="7">
+        <v>1</v>
+      </c>
+      <c r="E27" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="F27" s="11"/>
+      <c r="G27" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="H27" s="15"/>
     </row>
     <row r="28" spans="2:8" ht="18.75">
-      <c r="B28" s="3" t="s">
-        <v>111</v>
-      </c>
-      <c r="C28" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="D28" s="8">
-        <v>5</v>
-      </c>
-      <c r="E28" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="F28" s="10"/>
-      <c r="G28" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="H28" s="14" t="s">
-        <v>65</v>
-      </c>
+      <c r="B28" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="D28" s="7">
+        <v>2</v>
+      </c>
+      <c r="E28" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="F28" s="11"/>
+      <c r="G28" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="H28" s="15"/>
     </row>
     <row r="29" spans="2:8" ht="18.75">
       <c r="B29" s="1" t="s">
-        <v>111</v>
+        <v>24</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>66</v>
+        <v>95</v>
       </c>
       <c r="D29" s="7">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E29" s="5" t="s">
         <v>8</v>
@@ -2233,19 +2309,17 @@
       <c r="G29" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="H29" s="15" t="s">
-        <v>122</v>
-      </c>
+      <c r="H29" s="15"/>
     </row>
     <row r="30" spans="2:8" ht="18.75">
       <c r="B30" s="1" t="s">
-        <v>111</v>
+        <v>24</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>67</v>
+        <v>99</v>
       </c>
       <c r="D30" s="7">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E30" s="5" t="s">
         <v>8</v>
@@ -2254,106 +2328,102 @@
       <c r="G30" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="H30" s="15" t="s">
-        <v>123</v>
-      </c>
+      <c r="H30" s="15"/>
     </row>
     <row r="31" spans="2:8" ht="18.75">
       <c r="B31" s="1" t="s">
-        <v>111</v>
+        <v>24</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>69</v>
+        <v>85</v>
       </c>
       <c r="D31" s="7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E31" s="5" t="s">
         <v>8</v>
       </c>
       <c r="F31" s="11"/>
       <c r="G31" s="11" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H31" s="15"/>
     </row>
     <row r="32" spans="2:8" ht="18.75">
-      <c r="B32" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="C32" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="D32" s="7">
-        <v>4</v>
-      </c>
-      <c r="E32" s="5" t="s">
-        <v>8</v>
-      </c>
+      <c r="B32" s="1"/>
+      <c r="C32" s="1"/>
+      <c r="D32" s="7"/>
+      <c r="E32" s="5"/>
       <c r="F32" s="11"/>
-      <c r="G32" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="H32" s="15" t="s">
-        <v>71</v>
-      </c>
+      <c r="G32" s="11"/>
+      <c r="H32" s="15"/>
     </row>
     <row r="33" spans="2:8" ht="18.75">
-      <c r="B33" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="C33" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="D33" s="7">
-        <v>3</v>
-      </c>
-      <c r="E33" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="F33" s="11"/>
-      <c r="G33" s="11" t="s">
-        <v>9</v>
-      </c>
-      <c r="H33" s="15"/>
+      <c r="B33" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="C33" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="D33" s="8">
+        <v>1</v>
+      </c>
+      <c r="E33" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F33" s="10"/>
+      <c r="G33" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="H33" s="43"/>
     </row>
     <row r="34" spans="2:8" ht="18.75">
       <c r="B34" s="1" t="s">
-        <v>111</v>
+        <v>25</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="D34" s="7">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="E34" s="5" t="s">
         <v>8</v>
       </c>
       <c r="F34" s="11"/>
       <c r="G34" s="11" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H34" s="15"/>
     </row>
     <row r="35" spans="2:8" ht="18.75">
-      <c r="B35" s="2"/>
-      <c r="C35" s="2"/>
-      <c r="D35" s="7"/>
-      <c r="E35" s="6"/>
-      <c r="F35" s="12"/>
-      <c r="G35" s="12"/>
-      <c r="H35" s="16"/>
+      <c r="B35" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C35" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="D35" s="7">
+        <v>2</v>
+      </c>
+      <c r="E35" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="F35" s="11"/>
+      <c r="G35" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="H35" s="15"/>
     </row>
     <row r="36" spans="2:8" ht="18.75">
       <c r="B36" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="D36" s="4">
-        <v>1.5</v>
+        <v>95</v>
+      </c>
+      <c r="D36" s="7">
+        <v>2</v>
       </c>
       <c r="E36" s="5" t="s">
         <v>8</v>
@@ -2366,13 +2436,13 @@
     </row>
     <row r="37" spans="2:8" ht="18.75">
       <c r="B37" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>74</v>
+        <v>99</v>
       </c>
       <c r="D37" s="7">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E37" s="5" t="s">
         <v>8</v>
@@ -2385,51 +2455,41 @@
     </row>
     <row r="38" spans="2:8" ht="18.75">
       <c r="B38" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>73</v>
+        <v>85</v>
       </c>
       <c r="D38" s="7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E38" s="5" t="s">
         <v>8</v>
       </c>
       <c r="F38" s="11"/>
       <c r="G38" s="11" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H38" s="15"/>
     </row>
     <row r="39" spans="2:8" ht="18.75">
-      <c r="B39" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="C39" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="D39" s="7">
-        <v>2</v>
-      </c>
-      <c r="E39" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="F39" s="11"/>
-      <c r="G39" s="11" t="s">
-        <v>9</v>
-      </c>
-      <c r="H39" s="15"/>
+      <c r="B39" s="2"/>
+      <c r="C39" s="2"/>
+      <c r="D39" s="7"/>
+      <c r="E39" s="6"/>
+      <c r="F39" s="12"/>
+      <c r="G39" s="12"/>
+      <c r="H39" s="16"/>
     </row>
     <row r="40" spans="2:8" ht="18.75">
       <c r="B40" s="1" t="s">
-        <v>24</v>
+        <v>63</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="D40" s="7">
-        <v>3</v>
+        <v>77</v>
+      </c>
+      <c r="D40" s="4">
+        <v>1.5</v>
       </c>
       <c r="E40" s="5" t="s">
         <v>8</v>
@@ -2442,10 +2502,10 @@
     </row>
     <row r="41" spans="2:8" ht="18.75">
       <c r="B41" s="1" t="s">
-        <v>24</v>
+        <v>63</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>85</v>
+        <v>74</v>
       </c>
       <c r="D41" s="7">
         <v>1</v>
@@ -2455,47 +2515,57 @@
       </c>
       <c r="F41" s="11"/>
       <c r="G41" s="11" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H41" s="15"/>
     </row>
     <row r="42" spans="2:8" ht="18.75">
-      <c r="B42" s="1"/>
-      <c r="C42" s="1"/>
-      <c r="D42" s="7"/>
-      <c r="E42" s="5"/>
+      <c r="B42" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="C42" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="D42" s="7">
+        <v>2</v>
+      </c>
+      <c r="E42" s="5" t="s">
+        <v>8</v>
+      </c>
       <c r="F42" s="11"/>
-      <c r="G42" s="11"/>
+      <c r="G42" s="11" t="s">
+        <v>12</v>
+      </c>
       <c r="H42" s="15"/>
     </row>
     <row r="43" spans="2:8" ht="18.75">
-      <c r="B43" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="C43" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="D43" s="8">
-        <v>1</v>
-      </c>
-      <c r="E43" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="F43" s="10"/>
-      <c r="G43" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="H43" s="43"/>
+      <c r="B43" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="C43" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="D43" s="7">
+        <v>2</v>
+      </c>
+      <c r="E43" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="F43" s="11"/>
+      <c r="G43" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="H43" s="15"/>
     </row>
     <row r="44" spans="2:8" ht="18.75">
       <c r="B44" s="1" t="s">
-        <v>25</v>
+        <v>63</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>76</v>
+        <v>99</v>
       </c>
       <c r="D44" s="7">
-        <v>1.5</v>
+        <v>3</v>
       </c>
       <c r="E44" s="5" t="s">
         <v>8</v>
@@ -2508,98 +2578,98 @@
     </row>
     <row r="45" spans="2:8" ht="18.75">
       <c r="B45" s="1" t="s">
-        <v>25</v>
+        <v>63</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>73</v>
+        <v>85</v>
       </c>
       <c r="D45" s="7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E45" s="5" t="s">
         <v>8</v>
       </c>
       <c r="F45" s="11"/>
       <c r="G45" s="11" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H45" s="15"/>
     </row>
     <row r="46" spans="2:8" ht="18.75">
-      <c r="B46" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="C46" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="D46" s="7">
-        <v>2</v>
-      </c>
-      <c r="E46" s="5" t="s">
-        <v>8</v>
-      </c>
+      <c r="B46" s="1"/>
+      <c r="C46" s="1"/>
+      <c r="D46" s="7"/>
+      <c r="E46" s="5"/>
       <c r="F46" s="11"/>
-      <c r="G46" s="11" t="s">
-        <v>9</v>
-      </c>
+      <c r="G46" s="11"/>
       <c r="H46" s="15"/>
     </row>
     <row r="47" spans="2:8" ht="18.75">
-      <c r="B47" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="C47" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="D47" s="7">
-        <v>3</v>
-      </c>
-      <c r="E47" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="F47" s="11"/>
-      <c r="G47" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="H47" s="15"/>
+      <c r="B47" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="C47" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="D47" s="8">
+        <v>5</v>
+      </c>
+      <c r="E47" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F47" s="10"/>
+      <c r="G47" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="H47" s="14"/>
     </row>
     <row r="48" spans="2:8" ht="18.75">
       <c r="B48" s="1" t="s">
-        <v>25</v>
+        <v>52</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="D48" s="7">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E48" s="5" t="s">
         <v>8</v>
       </c>
       <c r="F48" s="11"/>
       <c r="G48" s="11" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H48" s="15"/>
     </row>
     <row r="49" spans="2:8" ht="18.75">
-      <c r="B49" s="2"/>
-      <c r="C49" s="2"/>
-      <c r="D49" s="7"/>
-      <c r="E49" s="6"/>
-      <c r="F49" s="12"/>
-      <c r="G49" s="12"/>
-      <c r="H49" s="16"/>
+      <c r="B49" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="C49" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="D49" s="7">
+        <v>1</v>
+      </c>
+      <c r="E49" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="F49" s="11"/>
+      <c r="G49" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="H49" s="15"/>
     </row>
     <row r="50" spans="2:8" ht="18.75">
       <c r="B50" s="1" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="D50" s="4">
-        <v>1.5</v>
+        <v>88</v>
+      </c>
+      <c r="D50" s="7">
+        <v>5</v>
       </c>
       <c r="E50" s="5" t="s">
         <v>8</v>
@@ -2608,33 +2678,35 @@
       <c r="G50" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="H50" s="15"/>
+      <c r="H50" s="15" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="51" spans="2:8" ht="18.75">
       <c r="B51" s="1" t="s">
-        <v>63</v>
+        <v>52</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D51" s="7">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E51" s="5" t="s">
         <v>8</v>
       </c>
       <c r="F51" s="11"/>
       <c r="G51" s="11" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H51" s="15"/>
     </row>
     <row r="52" spans="2:8" ht="18.75">
       <c r="B52" s="1" t="s">
-        <v>63</v>
+        <v>52</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>73</v>
+        <v>95</v>
       </c>
       <c r="D52" s="7">
         <v>2</v>
@@ -2644,179 +2716,169 @@
       </c>
       <c r="F52" s="11"/>
       <c r="G52" s="11" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H52" s="15"/>
     </row>
     <row r="53" spans="2:8" ht="18.75">
       <c r="B53" s="1" t="s">
-        <v>63</v>
+        <v>52</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="D53" s="7">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E53" s="5" t="s">
         <v>8</v>
       </c>
       <c r="F53" s="11"/>
       <c r="G53" s="11" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="H53" s="15"/>
     </row>
     <row r="54" spans="2:8" ht="18.75">
       <c r="B54" s="1" t="s">
-        <v>63</v>
+        <v>52</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>99</v>
+        <v>85</v>
       </c>
       <c r="D54" s="7">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E54" s="5" t="s">
         <v>8</v>
       </c>
       <c r="F54" s="11"/>
       <c r="G54" s="11" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H54" s="15"/>
     </row>
     <row r="55" spans="2:8" ht="18.75">
-      <c r="B55" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="C55" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="D55" s="7">
-        <v>1</v>
-      </c>
-      <c r="E55" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="F55" s="11"/>
-      <c r="G55" s="11" t="s">
-        <v>11</v>
-      </c>
-      <c r="H55" s="15"/>
+      <c r="B55" s="2"/>
+      <c r="C55" s="2"/>
+      <c r="D55" s="7"/>
+      <c r="E55" s="6"/>
+      <c r="F55" s="12"/>
+      <c r="G55" s="12"/>
+      <c r="H55" s="16"/>
     </row>
     <row r="56" spans="2:8" ht="18.75">
-      <c r="B56" s="1"/>
-      <c r="C56" s="1"/>
-      <c r="D56" s="7"/>
-      <c r="E56" s="5"/>
+      <c r="B56" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="C56" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="D56" s="4">
+        <v>2</v>
+      </c>
+      <c r="E56" s="5" t="s">
+        <v>8</v>
+      </c>
       <c r="F56" s="11"/>
-      <c r="G56" s="11"/>
+      <c r="G56" s="11" t="s">
+        <v>12</v>
+      </c>
       <c r="H56" s="15"/>
     </row>
     <row r="57" spans="2:8" ht="18.75">
-      <c r="B57" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="C57" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="D57" s="8">
-        <v>5</v>
-      </c>
-      <c r="E57" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="F57" s="10"/>
-      <c r="G57" s="10" t="s">
-        <v>9</v>
-      </c>
-      <c r="H57" s="14"/>
+      <c r="B57" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="C57" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="D57" s="7">
+        <v>2</v>
+      </c>
+      <c r="E57" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="F57" s="11"/>
+      <c r="G57" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="H57" s="15"/>
     </row>
     <row r="58" spans="2:8" ht="18.75">
       <c r="B58" s="1" t="s">
-        <v>52</v>
+        <v>89</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="D58" s="7">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E58" s="5" t="s">
         <v>8</v>
       </c>
       <c r="F58" s="11"/>
       <c r="G58" s="11" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="H58" s="15"/>
     </row>
     <row r="59" spans="2:8" ht="18.75">
       <c r="B59" s="1" t="s">
-        <v>52</v>
+        <v>89</v>
       </c>
       <c r="C59" s="1" t="s">
-        <v>74</v>
+        <v>93</v>
       </c>
       <c r="D59" s="7">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E59" s="5" t="s">
         <v>8</v>
       </c>
       <c r="F59" s="11"/>
       <c r="G59" s="11" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="H59" s="15"/>
     </row>
     <row r="60" spans="2:8" ht="18.75">
-      <c r="B60" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="C60" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="D60" s="7">
-        <v>5</v>
-      </c>
-      <c r="E60" s="5" t="s">
-        <v>8</v>
-      </c>
+      <c r="B60" s="1"/>
+      <c r="C60" s="1"/>
+      <c r="D60" s="7"/>
+      <c r="E60" s="5"/>
       <c r="F60" s="11"/>
-      <c r="G60" s="11" t="s">
-        <v>9</v>
-      </c>
-      <c r="H60" s="15" t="s">
-        <v>27</v>
-      </c>
+      <c r="G60" s="11"/>
+      <c r="H60" s="15"/>
     </row>
     <row r="61" spans="2:8" ht="18.75">
-      <c r="B61" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="C61" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="D61" s="7">
-        <v>3</v>
-      </c>
-      <c r="E61" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="F61" s="11"/>
-      <c r="G61" s="11" t="s">
-        <v>9</v>
-      </c>
-      <c r="H61" s="15"/>
+      <c r="B61" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="C61" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D61" s="4">
+        <v>2</v>
+      </c>
+      <c r="E61" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F61" s="10"/>
+      <c r="G61" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="H61" s="14" t="s">
+        <v>30</v>
+      </c>
     </row>
     <row r="62" spans="2:8" ht="18.75">
       <c r="B62" s="1" t="s">
-        <v>52</v>
+        <v>98</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>95</v>
+        <v>31</v>
       </c>
       <c r="D62" s="7">
         <v>2</v>
@@ -2826,85 +2888,101 @@
       </c>
       <c r="F62" s="11"/>
       <c r="G62" s="11" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="H62" s="15"/>
     </row>
     <row r="63" spans="2:8" ht="18.75">
       <c r="B63" s="1" t="s">
-        <v>52</v>
+        <v>98</v>
       </c>
       <c r="C63" s="1" t="s">
-        <v>99</v>
+        <v>80</v>
       </c>
       <c r="D63" s="7">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E63" s="5" t="s">
         <v>8</v>
       </c>
       <c r="F63" s="11"/>
       <c r="G63" s="11" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="H63" s="15"/>
     </row>
     <row r="64" spans="2:8" ht="18.75">
       <c r="B64" s="1" t="s">
-        <v>52</v>
+        <v>98</v>
       </c>
       <c r="C64" s="1" t="s">
-        <v>85</v>
+        <v>32</v>
       </c>
       <c r="D64" s="7">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E64" s="5" t="s">
         <v>8</v>
       </c>
       <c r="F64" s="11"/>
       <c r="G64" s="11" t="s">
-        <v>9</v>
-      </c>
-      <c r="H64" s="15"/>
+        <v>12</v>
+      </c>
+      <c r="H64" s="15" t="s">
+        <v>33</v>
+      </c>
     </row>
     <row r="65" spans="2:8" ht="18.75">
-      <c r="B65" s="2"/>
-      <c r="C65" s="2"/>
-      <c r="D65" s="7"/>
-      <c r="E65" s="6"/>
-      <c r="F65" s="12"/>
-      <c r="G65" s="12"/>
-      <c r="H65" s="16"/>
+      <c r="B65" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="C65" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D65" s="7">
+        <v>4</v>
+      </c>
+      <c r="E65" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="F65" s="11"/>
+      <c r="G65" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="H65" s="15" t="s">
+        <v>96</v>
+      </c>
     </row>
     <row r="66" spans="2:8" ht="18.75">
       <c r="B66" s="1" t="s">
-        <v>89</v>
+        <v>98</v>
       </c>
       <c r="C66" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="D66" s="4">
-        <v>2</v>
+        <v>78</v>
+      </c>
+      <c r="D66" s="7">
+        <v>6</v>
       </c>
       <c r="E66" s="5" t="s">
         <v>8</v>
       </c>
       <c r="F66" s="11"/>
       <c r="G66" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="H66" s="15"/>
+        <v>9</v>
+      </c>
+      <c r="H66" s="15" t="s">
+        <v>83</v>
+      </c>
     </row>
     <row r="67" spans="2:8" ht="18.75">
       <c r="B67" s="1" t="s">
-        <v>89</v>
+        <v>98</v>
       </c>
       <c r="C67" s="1" t="s">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="D67" s="7">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E67" s="5" t="s">
         <v>8</v>
@@ -2917,10 +2995,10 @@
     </row>
     <row r="68" spans="2:8" ht="18.75">
       <c r="B68" s="1" t="s">
-        <v>89</v>
+        <v>98</v>
       </c>
       <c r="C68" s="1" t="s">
-        <v>92</v>
+        <v>124</v>
       </c>
       <c r="D68" s="7">
         <v>2</v>
@@ -2935,60 +3013,58 @@
       <c r="H68" s="15"/>
     </row>
     <row r="69" spans="2:8" ht="18.75">
-      <c r="B69" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="C69" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="D69" s="7">
+      <c r="B69" s="1"/>
+      <c r="C69" s="1"/>
+      <c r="D69" s="7"/>
+      <c r="E69" s="5"/>
+      <c r="F69" s="11"/>
+      <c r="G69" s="11"/>
+      <c r="H69" s="15"/>
+    </row>
+    <row r="70" spans="2:8" ht="18.75">
+      <c r="B70" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="C70" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="D70" s="8">
         <v>2</v>
       </c>
-      <c r="E69" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="F69" s="11"/>
-      <c r="G69" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="H69" s="15"/>
-    </row>
-    <row r="70" spans="2:8" ht="18.75">
-      <c r="B70" s="1"/>
-      <c r="C70" s="1"/>
-      <c r="D70" s="7"/>
-      <c r="E70" s="5"/>
-      <c r="F70" s="11"/>
-      <c r="G70" s="11"/>
-      <c r="H70" s="15"/>
+      <c r="E70" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F70" s="10"/>
+      <c r="G70" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="H70" s="14"/>
     </row>
     <row r="71" spans="2:8" ht="18.75">
-      <c r="B71" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="C71" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="D71" s="4">
+      <c r="B71" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C71" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="D71" s="7">
         <v>2</v>
       </c>
-      <c r="E71" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="F71" s="10"/>
-      <c r="G71" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="H71" s="14" t="s">
-        <v>30</v>
-      </c>
+      <c r="E71" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="F71" s="11"/>
+      <c r="G71" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="H71" s="15"/>
     </row>
     <row r="72" spans="2:8" ht="18.75">
       <c r="B72" s="1" t="s">
-        <v>98</v>
+        <v>35</v>
       </c>
       <c r="C72" s="1" t="s">
-        <v>31</v>
+        <v>54</v>
       </c>
       <c r="D72" s="7">
         <v>2</v>
@@ -3004,13 +3080,13 @@
     </row>
     <row r="73" spans="2:8" ht="18.75">
       <c r="B73" s="1" t="s">
-        <v>98</v>
+        <v>35</v>
       </c>
       <c r="C73" s="1" t="s">
-        <v>80</v>
+        <v>37</v>
       </c>
       <c r="D73" s="7">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E73" s="5" t="s">
         <v>8</v>
@@ -3023,13 +3099,13 @@
     </row>
     <row r="74" spans="2:8" ht="18.75">
       <c r="B74" s="1" t="s">
-        <v>98</v>
+        <v>35</v>
       </c>
       <c r="C74" s="1" t="s">
-        <v>32</v>
+        <v>102</v>
       </c>
       <c r="D74" s="7">
-        <v>4</v>
+        <v>0.5</v>
       </c>
       <c r="E74" s="5" t="s">
         <v>8</v>
@@ -3038,165 +3114,149 @@
       <c r="G74" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="H74" s="15" t="s">
-        <v>33</v>
-      </c>
+      <c r="H74" s="15"/>
     </row>
     <row r="75" spans="2:8" ht="18.75">
-      <c r="B75" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="C75" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="D75" s="7">
-        <v>4</v>
-      </c>
-      <c r="E75" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="F75" s="11"/>
-      <c r="G75" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="H75" s="15" t="s">
-        <v>96</v>
-      </c>
+      <c r="B75" s="2"/>
+      <c r="C75" s="2"/>
+      <c r="D75" s="7"/>
+      <c r="E75" s="6"/>
+      <c r="F75" s="12"/>
+      <c r="G75" s="12"/>
+      <c r="H75" s="16"/>
     </row>
     <row r="76" spans="2:8" ht="18.75">
       <c r="B76" s="1" t="s">
-        <v>98</v>
+        <v>38</v>
       </c>
       <c r="C76" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="D76" s="7">
-        <v>6</v>
+        <v>39</v>
+      </c>
+      <c r="D76" s="4">
+        <v>1</v>
       </c>
       <c r="E76" s="5" t="s">
         <v>8</v>
       </c>
       <c r="F76" s="11"/>
       <c r="G76" s="11" t="s">
-        <v>9</v>
-      </c>
-      <c r="H76" s="15" t="s">
-        <v>83</v>
-      </c>
+        <v>12</v>
+      </c>
+      <c r="H76" s="15"/>
     </row>
     <row r="77" spans="2:8" ht="18.75">
       <c r="B77" s="1" t="s">
-        <v>98</v>
+        <v>38</v>
       </c>
       <c r="C77" s="1" t="s">
-        <v>79</v>
+        <v>40</v>
       </c>
       <c r="D77" s="7">
-        <v>3</v>
+        <v>0.5</v>
       </c>
       <c r="E77" s="5" t="s">
         <v>8</v>
       </c>
       <c r="F77" s="11"/>
       <c r="G77" s="11" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H77" s="15"/>
     </row>
     <row r="78" spans="2:8" ht="18.75">
       <c r="B78" s="1" t="s">
-        <v>98</v>
+        <v>38</v>
       </c>
       <c r="C78" s="1" t="s">
-        <v>124</v>
+        <v>41</v>
       </c>
       <c r="D78" s="7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E78" s="5" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="F78" s="11"/>
       <c r="G78" s="11" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="H78" s="15"/>
     </row>
     <row r="79" spans="2:8" ht="18.75">
-      <c r="B79" s="1"/>
-      <c r="C79" s="1"/>
-      <c r="D79" s="7"/>
-      <c r="E79" s="5"/>
+      <c r="B79" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="C79" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="D79" s="7">
+        <v>1</v>
+      </c>
+      <c r="E79" s="5" t="s">
+        <v>13</v>
+      </c>
       <c r="F79" s="11"/>
-      <c r="G79" s="11"/>
+      <c r="G79" s="11" t="s">
+        <v>12</v>
+      </c>
       <c r="H79" s="15"/>
     </row>
     <row r="80" spans="2:8" ht="18.75">
-      <c r="B80" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="C80" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="D80" s="8">
-        <v>2</v>
-      </c>
-      <c r="E80" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="F80" s="10"/>
-      <c r="G80" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="H80" s="14"/>
+      <c r="B80" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="C80" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="D80" s="7">
+        <v>0.5</v>
+      </c>
+      <c r="E80" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="F80" s="11"/>
+      <c r="G80" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="H80" s="15"/>
     </row>
     <row r="81" spans="2:8" ht="18.75">
-      <c r="B81" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="C81" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="D81" s="7">
-        <v>2</v>
-      </c>
-      <c r="E81" s="5" t="s">
-        <v>8</v>
-      </c>
+      <c r="B81" s="1"/>
+      <c r="C81" s="1"/>
+      <c r="D81" s="7"/>
+      <c r="E81" s="5"/>
       <c r="F81" s="11"/>
-      <c r="G81" s="11" t="s">
-        <v>12</v>
-      </c>
+      <c r="G81" s="11"/>
       <c r="H81" s="15"/>
     </row>
     <row r="82" spans="2:8" ht="18.75">
-      <c r="B82" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="C82" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="D82" s="7">
-        <v>2</v>
-      </c>
-      <c r="E82" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="F82" s="11"/>
-      <c r="G82" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="H82" s="15"/>
+      <c r="B82" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="C82" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="D82" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="E82" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F82" s="10"/>
+      <c r="G82" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="H82" s="14"/>
     </row>
     <row r="83" spans="2:8" ht="18.75">
       <c r="B83" s="1" t="s">
-        <v>35</v>
+        <v>100</v>
       </c>
       <c r="C83" s="1" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="D83" s="7">
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="E83" s="5" t="s">
         <v>8</v>
@@ -3209,16 +3269,16 @@
     </row>
     <row r="84" spans="2:8" ht="18.75">
       <c r="B84" s="1" t="s">
-        <v>35</v>
+        <v>100</v>
       </c>
       <c r="C84" s="1" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="D84" s="7">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="E84" s="5" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="F84" s="11"/>
       <c r="G84" s="11" t="s">
@@ -3227,83 +3287,89 @@
       <c r="H84" s="15"/>
     </row>
     <row r="85" spans="2:8" ht="18.75">
-      <c r="B85" s="2"/>
-      <c r="C85" s="2"/>
-      <c r="D85" s="7"/>
-      <c r="E85" s="6"/>
-      <c r="F85" s="12"/>
-      <c r="G85" s="12"/>
-      <c r="H85" s="16"/>
+      <c r="B85" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="C85" s="47" t="s">
+        <v>104</v>
+      </c>
+      <c r="D85" s="7">
+        <v>1</v>
+      </c>
+      <c r="E85" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="F85" s="11"/>
+      <c r="G85" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="H85" s="15" t="s">
+        <v>105</v>
+      </c>
     </row>
     <row r="86" spans="2:8" ht="18.75">
       <c r="B86" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="C86" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="D86" s="4">
+        <v>101</v>
+      </c>
+      <c r="C86" s="51" t="s">
+        <v>125</v>
+      </c>
+      <c r="D86" s="50">
         <v>1</v>
       </c>
-      <c r="E86" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="F86" s="11"/>
-      <c r="G86" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="H86" s="15"/>
+      <c r="E86" s="50" t="s">
+        <v>8</v>
+      </c>
+      <c r="F86" s="50"/>
+      <c r="G86" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="H86" s="15" t="s">
+        <v>117</v>
+      </c>
     </row>
     <row r="87" spans="2:8" ht="18.75">
-      <c r="B87" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="C87" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="D87" s="7">
-        <v>0.5</v>
-      </c>
-      <c r="E87" s="5" t="s">
-        <v>8</v>
-      </c>
+      <c r="B87" s="1"/>
+      <c r="C87" s="1"/>
+      <c r="D87" s="7"/>
+      <c r="E87" s="5"/>
       <c r="F87" s="11"/>
-      <c r="G87" s="11" t="s">
-        <v>12</v>
-      </c>
+      <c r="G87" s="11"/>
       <c r="H87" s="15"/>
     </row>
     <row r="88" spans="2:8" ht="18.75">
-      <c r="B88" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="C88" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="D88" s="7">
-        <v>1</v>
-      </c>
-      <c r="E88" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="F88" s="11"/>
-      <c r="G88" s="11" t="s">
+      <c r="B88" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="C88" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="D88" s="4">
+        <v>2</v>
+      </c>
+      <c r="E88" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F88" s="4"/>
+      <c r="G88" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="H88" s="15"/>
+      <c r="H88" s="14" t="s">
+        <v>44</v>
+      </c>
     </row>
     <row r="89" spans="2:8" ht="18.75">
       <c r="B89" s="1" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="C89" s="1" t="s">
-        <v>116</v>
+        <v>45</v>
       </c>
       <c r="D89" s="7">
         <v>1</v>
       </c>
       <c r="E89" s="5" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="F89" s="11"/>
       <c r="G89" s="11" t="s">
@@ -3313,353 +3379,227 @@
     </row>
     <row r="90" spans="2:8" ht="18.75">
       <c r="B90" s="1" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="C90" s="1" t="s">
-        <v>102</v>
+        <v>46</v>
       </c>
       <c r="D90" s="7">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="E90" s="5" t="s">
         <v>8</v>
       </c>
       <c r="F90" s="11"/>
       <c r="G90" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="H90" s="15"/>
+        <v>9</v>
+      </c>
+      <c r="H90" s="15" t="s">
+        <v>62</v>
+      </c>
     </row>
     <row r="91" spans="2:8" ht="18.75">
-      <c r="B91" s="1"/>
-      <c r="C91" s="1"/>
-      <c r="D91" s="7"/>
-      <c r="E91" s="5"/>
+      <c r="B91" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="C91" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="D91" s="7">
+        <v>0.5</v>
+      </c>
+      <c r="E91" s="5" t="s">
+        <v>8</v>
+      </c>
       <c r="F91" s="11"/>
-      <c r="G91" s="11"/>
+      <c r="G91" s="11" t="s">
+        <v>9</v>
+      </c>
       <c r="H91" s="15"/>
     </row>
     <row r="92" spans="2:8" ht="18.75">
-      <c r="B92" s="3" t="s">
-        <v>101</v>
-      </c>
-      <c r="C92" s="3" t="s">
-        <v>102</v>
-      </c>
-      <c r="D92" s="8">
-        <v>0.5</v>
-      </c>
-      <c r="E92" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="F92" s="10"/>
-      <c r="G92" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="H92" s="14"/>
+      <c r="B92" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="C92" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="D92" s="7">
+        <v>1</v>
+      </c>
+      <c r="E92" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="F92" s="11"/>
+      <c r="G92" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="H92" s="15"/>
     </row>
     <row r="93" spans="2:8" ht="18.75">
       <c r="B93" s="1" t="s">
-        <v>100</v>
+        <v>42</v>
       </c>
       <c r="C93" s="1" t="s">
-        <v>40</v>
+        <v>116</v>
       </c>
       <c r="D93" s="7">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="E93" s="5" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="F93" s="11"/>
       <c r="G93" s="11" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="H93" s="15"/>
     </row>
     <row r="94" spans="2:8" ht="18.75">
-      <c r="B94" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="C94" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="D94" s="7">
-        <v>1</v>
-      </c>
-      <c r="E94" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="F94" s="11"/>
-      <c r="G94" s="11" t="s">
-        <v>9</v>
-      </c>
-      <c r="H94" s="15"/>
+      <c r="B94" s="2"/>
+      <c r="C94" s="2"/>
+      <c r="D94" s="7"/>
+      <c r="E94" s="6"/>
+      <c r="F94" s="12"/>
+      <c r="G94" s="12"/>
+      <c r="H94" s="16"/>
     </row>
     <row r="95" spans="2:8" ht="18.75">
       <c r="B95" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="C95" s="47" t="s">
-        <v>104</v>
-      </c>
-      <c r="D95" s="7">
-        <v>1</v>
-      </c>
-      <c r="E95" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="F95" s="11"/>
-      <c r="G95" s="11" t="s">
-        <v>9</v>
-      </c>
-      <c r="H95" s="15" t="s">
-        <v>105</v>
-      </c>
+        <v>115</v>
+      </c>
+      <c r="C95" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="D95" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="E95" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F95" s="10"/>
+      <c r="G95" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="H95" s="15"/>
     </row>
     <row r="96" spans="2:8" ht="18.75">
       <c r="B96" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="C96" s="51" t="s">
-        <v>125</v>
-      </c>
-      <c r="D96" s="50">
+        <v>114</v>
+      </c>
+      <c r="C96" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="D96" s="7">
+        <v>0.5</v>
+      </c>
+      <c r="E96" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="F96" s="11"/>
+      <c r="G96" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="H96" s="15"/>
+    </row>
+    <row r="97" spans="2:8" ht="18.75">
+      <c r="B97" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="C97" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="D97" s="7">
         <v>1</v>
       </c>
-      <c r="E96" s="50" t="s">
-        <v>8</v>
-      </c>
-      <c r="F96" s="50"/>
-      <c r="G96" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="H96" s="15" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="97" spans="2:8" ht="18.75">
-      <c r="B97" s="1"/>
-      <c r="C97" s="1"/>
-      <c r="D97" s="7"/>
-      <c r="E97" s="5"/>
+      <c r="E97" s="5" t="s">
+        <v>13</v>
+      </c>
       <c r="F97" s="11"/>
-      <c r="G97" s="11"/>
+      <c r="G97" s="11" t="s">
+        <v>12</v>
+      </c>
       <c r="H97" s="15"/>
     </row>
     <row r="98" spans="2:8" ht="18.75">
-      <c r="B98" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="C98" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="D98" s="4">
-        <v>2</v>
-      </c>
-      <c r="E98" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F98" s="4"/>
-      <c r="G98" s="10" t="s">
-        <v>9</v>
-      </c>
-      <c r="H98" s="14" t="s">
-        <v>44</v>
+      <c r="B98" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="C98" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="D98" s="7">
+        <v>1</v>
+      </c>
+      <c r="E98" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="F98" s="11"/>
+      <c r="G98" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="H98" s="15" t="s">
+        <v>118</v>
       </c>
     </row>
     <row r="99" spans="2:8" ht="18.75">
-      <c r="B99" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="C99" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="D99" s="7">
-        <v>1</v>
-      </c>
-      <c r="E99" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="F99" s="11"/>
-      <c r="G99" s="11" t="s">
-        <v>9</v>
-      </c>
-      <c r="H99" s="15"/>
+      <c r="B99" s="2"/>
+      <c r="C99" s="2"/>
+      <c r="D99" s="9"/>
+      <c r="E99" s="6"/>
+      <c r="F99" s="12"/>
+      <c r="G99" s="12"/>
+      <c r="H99" s="16"/>
     </row>
     <row r="100" spans="2:8" ht="18.75">
-      <c r="B100" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="C100" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="D100" s="7">
-        <v>1</v>
-      </c>
-      <c r="E100" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="F100" s="11"/>
-      <c r="G100" s="11" t="s">
-        <v>9</v>
-      </c>
-      <c r="H100" s="15" t="s">
-        <v>62</v>
-      </c>
+      <c r="C100"/>
+      <c r="D100" s="7"/>
+      <c r="H100" s="13"/>
     </row>
     <row r="101" spans="2:8" ht="18.75">
-      <c r="B101" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="C101" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="D101" s="7">
-        <v>0.5</v>
-      </c>
-      <c r="E101" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="F101" s="11"/>
-      <c r="G101" s="11" t="s">
-        <v>9</v>
-      </c>
-      <c r="H101" s="15"/>
+      <c r="C101"/>
+      <c r="D101" s="7"/>
+      <c r="H101" s="13"/>
     </row>
     <row r="102" spans="2:8" ht="18.75">
-      <c r="B102" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="C102" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="D102" s="7">
-        <v>1</v>
-      </c>
-      <c r="E102" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="F102" s="11"/>
-      <c r="G102" s="11" t="s">
-        <v>9</v>
-      </c>
-      <c r="H102" s="15"/>
+      <c r="C102"/>
+      <c r="D102" s="7"/>
+      <c r="H102" s="13"/>
     </row>
     <row r="103" spans="2:8" ht="18.75">
-      <c r="B103" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="C103" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="D103" s="7">
-        <v>1</v>
-      </c>
-      <c r="E103" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="F103" s="11"/>
-      <c r="G103" s="11" t="s">
-        <v>9</v>
-      </c>
-      <c r="H103" s="15"/>
+      <c r="C103"/>
+      <c r="D103" s="7"/>
+      <c r="H103" s="13"/>
     </row>
     <row r="104" spans="2:8" ht="18.75">
-      <c r="B104" s="2"/>
-      <c r="C104" s="2"/>
+      <c r="C104"/>
       <c r="D104" s="7"/>
-      <c r="E104" s="6"/>
-      <c r="F104" s="12"/>
-      <c r="G104" s="12"/>
-      <c r="H104" s="16"/>
+      <c r="H104" s="13"/>
     </row>
     <row r="105" spans="2:8" ht="18.75">
-      <c r="B105" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="C105" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="D105" s="8">
-        <v>0.5</v>
-      </c>
-      <c r="E105" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="F105" s="10"/>
-      <c r="G105" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="H105" s="15"/>
+      <c r="C105"/>
+      <c r="D105" s="7"/>
+      <c r="H105" s="13"/>
     </row>
     <row r="106" spans="2:8" ht="18.75">
-      <c r="B106" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="C106" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="D106" s="7">
-        <v>0.5</v>
-      </c>
-      <c r="E106" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="F106" s="11"/>
-      <c r="G106" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="H106" s="15"/>
+      <c r="C106"/>
+      <c r="D106" s="7"/>
+      <c r="H106" s="13"/>
     </row>
     <row r="107" spans="2:8" ht="18.75">
-      <c r="B107" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="C107" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="D107" s="7">
-        <v>1</v>
-      </c>
-      <c r="E107" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="F107" s="11"/>
-      <c r="G107" s="11" t="s">
-        <v>9</v>
-      </c>
-      <c r="H107" s="15"/>
+      <c r="C107"/>
+      <c r="D107" s="7"/>
+      <c r="H107" s="13"/>
     </row>
     <row r="108" spans="2:8" ht="18.75">
-      <c r="B108" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="C108" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="D108" s="7">
-        <v>1</v>
-      </c>
-      <c r="E108" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="F108" s="11"/>
-      <c r="G108" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="H108" s="15" t="s">
-        <v>118</v>
-      </c>
+      <c r="C108"/>
+      <c r="D108" s="7"/>
+      <c r="H108" s="13"/>
     </row>
     <row r="109" spans="2:8" ht="18.75">
-      <c r="B109" s="2"/>
-      <c r="C109" s="2"/>
-      <c r="D109" s="9"/>
-      <c r="E109" s="6"/>
-      <c r="F109" s="12"/>
-      <c r="G109" s="12"/>
-      <c r="H109" s="16"/>
+      <c r="C109"/>
+      <c r="D109" s="7"/>
+      <c r="H109" s="13"/>
     </row>
     <row r="110" spans="2:8" ht="18.75">
       <c r="C110"/>
@@ -3671,26 +3611,10 @@
       <c r="D111" s="7"/>
       <c r="H111" s="13"/>
     </row>
-    <row r="112" spans="2:8" ht="18.75">
-      <c r="C112"/>
-      <c r="D112" s="7"/>
-      <c r="H112" s="13"/>
-    </row>
-    <row r="113" spans="3:8" ht="18.75">
-      <c r="C113"/>
-      <c r="D113" s="7"/>
-      <c r="H113" s="13"/>
-    </row>
-    <row r="114" spans="3:8" ht="18.75">
-      <c r="C114"/>
-      <c r="D114" s="7"/>
-      <c r="H114" s="13"/>
-    </row>
-    <row r="115" spans="3:8" ht="18.75">
-      <c r="C115"/>
-      <c r="D115" s="7"/>
-      <c r="H115" s="13"/>
-    </row>
+    <row r="112" spans="2:8" ht="18.75"/>
+    <row r="113" spans="3:8" ht="18.75"/>
+    <row r="114" spans="3:8" ht="18.75"/>
+    <row r="115" spans="3:8" ht="18.75"/>
     <row r="116" spans="3:8" ht="18.75">
       <c r="C116"/>
       <c r="D116" s="7"/>
@@ -3702,8 +3626,6 @@
       <c r="H117" s="13"/>
     </row>
     <row r="118" spans="3:8" ht="18.75">
-      <c r="C118"/>
-      <c r="D118" s="7"/>
       <c r="H118" s="13"/>
     </row>
     <row r="119" spans="3:8" ht="18.75">
@@ -3721,45 +3643,13 @@
       <c r="D121" s="7"/>
       <c r="H121" s="13"/>
     </row>
-    <row r="122" spans="3:8" ht="18.75"/>
-    <row r="123" spans="3:8" ht="18.75"/>
-    <row r="124" spans="3:8" ht="18.75"/>
-    <row r="125" spans="3:8" ht="18.75"/>
-    <row r="126" spans="3:8" ht="18.75">
-      <c r="C126"/>
-      <c r="D126" s="7"/>
-      <c r="H126" s="13"/>
-    </row>
-    <row r="127" spans="3:8" ht="18.75">
-      <c r="C127"/>
-      <c r="D127" s="7"/>
-      <c r="H127" s="13"/>
-    </row>
-    <row r="128" spans="3:8" ht="18.75">
-      <c r="H128" s="13"/>
-    </row>
-    <row r="129" spans="3:8" ht="18.75">
-      <c r="C129"/>
-      <c r="D129" s="7"/>
-      <c r="H129" s="13"/>
-    </row>
-    <row r="130" spans="3:8" ht="18.75">
-      <c r="C130"/>
-      <c r="D130" s="7"/>
-      <c r="H130" s="13"/>
-    </row>
-    <row r="131" spans="3:8" ht="18.75">
-      <c r="C131"/>
-      <c r="D131" s="7"/>
-      <c r="H131" s="13"/>
-    </row>
-    <row r="132" spans="3:8" ht="18.75">
-      <c r="C132"/>
-      <c r="D132" s="7"/>
-      <c r="H132" s="13"/>
+    <row r="122" spans="3:8" ht="18.75">
+      <c r="C122"/>
+      <c r="D122" s="7"/>
+      <c r="H122" s="13"/>
     </row>
   </sheetData>
-  <autoFilter ref="E2:G132" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter ref="E2:G122" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="1200" verticalDpi="1200"/>
@@ -3770,19 +3660,19 @@
           <x14:formula1>
             <xm:f>プルダウン用!$B$3:$B$6</xm:f>
           </x14:formula1>
-          <xm:sqref>G126:G127 G129:G1048576 G1:G26 G28:G121</xm:sqref>
+          <xm:sqref>G116:G117 G119:G1048576 G18:G111 G1:G16</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{66D8840C-D443-486F-BC72-01200775D285}">
           <x14:formula1>
             <xm:f>プルダウン用!$D$3:$D$6</xm:f>
           </x14:formula1>
-          <xm:sqref>F1:F2 F129:F1048576 F127 F3:F126</xm:sqref>
+          <xm:sqref>F119:F1048576 F1:F117</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{D61B1C0A-2748-4606-B0EE-00EEC89A23C6}">
           <x14:formula1>
             <xm:f>プルダウン用!$F$3:$F$6</xm:f>
           </x14:formula1>
-          <xm:sqref>E126:E127 E129:E1048576 E1:E26 E28:E121</xm:sqref>
+          <xm:sqref>E116:E117 E119:E1048576 E18:E111 E1:E16</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -3847,26 +3737,26 @@
       </c>
       <c r="D3" s="49">
         <f>SUMIFS(コスト表!D:D, コスト表!B:B, "プレイヤー", コスト表!G:G, "完了")</f>
-        <v>6.5</v>
+        <v>16</v>
       </c>
       <c r="E3" s="49">
         <f>SUMIFS(コスト表!D:D, コスト表!B:B, "プレイヤー", コスト表!G:G, "作業中")</f>
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F3" s="49">
         <f>SUMIFS(コスト表!D:D, コスト表!B:B, "プレイヤー", コスト表!G:G, "未着手")</f>
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="G3" s="38">
         <f>ROUNDDOWN(COUNTIFS(コスト表!B:B, "プレイヤー", コスト表!G:G, "完了") / COUNTIF(コスト表!B:B, "プレイヤー") * 100,1)</f>
-        <v>33.299999999999997</v>
+        <v>92.8</v>
       </c>
       <c r="I3" s="29" t="s">
         <v>17</v>
       </c>
       <c r="J3" s="27">
         <f>SUMIF(コスト表!G:G,"完了",コスト表!D:D)</f>
-        <v>88.5</v>
+        <v>127</v>
       </c>
       <c r="K3" s="26" t="s">
         <v>18</v>
@@ -3887,11 +3777,11 @@
       </c>
       <c r="E4" s="49">
         <f>SUMIFS(コスト表!D:D, コスト表!B:B, "敵ベース", コスト表!G:G, "作業中")</f>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F4" s="49">
         <f>SUMIFS(コスト表!D:D, コスト表!B:B, "敵ベース", コスト表!G:G, "未着手")</f>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G4" s="38">
         <f>ROUNDDOWN(COUNTIFS(コスト表!B:B, "敵ベース", コスト表!G:G, "完了") / COUNTIF(コスト表!B:B, "敵ベース") * 100,1)</f>
@@ -3902,11 +3792,11 @@
       </c>
       <c r="J4" s="27">
         <f ca="1">NETWORKDAYS(J5,J6)</f>
-        <v>29</v>
+        <v>90</v>
       </c>
       <c r="K4" s="27">
         <f ca="1" xml:space="preserve"> ROUNDDOWN(J3 / J4,1)</f>
-        <v>3</v>
+        <v>1.4</v>
       </c>
       <c r="M4" s="26"/>
     </row>
@@ -3920,7 +3810,7 @@
       </c>
       <c r="D5" s="49">
         <f>SUMIFS(コスト表!D:D, コスト表!B:B, "敵1(通常ゾンビ)", コスト表!G:G, "完了")</f>
-        <v>7.5</v>
+        <v>9.5</v>
       </c>
       <c r="E5" s="49">
         <f>SUMIFS(コスト表!D:D, コスト表!B:B, "敵1(通常ゾンビ)", コスト表!G:G, "作業中")</f>
@@ -3928,11 +3818,11 @@
       </c>
       <c r="F5" s="49">
         <f>SUMIFS(コスト表!D:D, コスト表!B:B, "敵1(通常ゾンビ)", コスト表!G:G, "未着手")</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G5" s="38">
         <f>ROUNDDOWN(COUNTIFS(コスト表!B:B, "敵1(通常ゾンビ)", コスト表!G:G, "完了") / COUNTIF(コスト表!B:B, "敵1(通常ゾンビ)") * 100,1)</f>
-        <v>66.599999999999994</v>
+        <v>83.3</v>
       </c>
       <c r="I5" s="31" t="s">
         <v>20</v>
@@ -3955,7 +3845,7 @@
       </c>
       <c r="D6" s="49">
         <f>SUMIFS(コスト表!D:D, コスト表!B:B, "敵2(ランナーゾンビ)", コスト表!G:G, "完了")</f>
-        <v>7.5</v>
+        <v>9.5</v>
       </c>
       <c r="E6" s="49">
         <f>SUMIFS(コスト表!D:D, コスト表!B:B, "敵2(ランナーゾンビ)", コスト表!G:G, "作業中")</f>
@@ -3963,18 +3853,18 @@
       </c>
       <c r="F6" s="49">
         <f>SUMIFS(コスト表!D:D,コスト表!B:B,"敵2(ランナーゾンビ)",コスト表!G:G,"未着手")</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G6" s="38">
         <f>ROUNDDOWN(COUNTIFS(コスト表!B:B, "敵2(ランナーゾンビ)", コスト表!G:G, "完了") / COUNTIF(コスト表!B:B, "敵2(ランナーゾンビ)") * 100,1)</f>
-        <v>66.599999999999994</v>
+        <v>83.3</v>
       </c>
       <c r="I6" s="32" t="s">
         <v>21</v>
       </c>
       <c r="J6" s="44">
         <f ca="1">TODAY()</f>
-        <v>45971</v>
+        <v>46056</v>
       </c>
       <c r="K6" s="44"/>
       <c r="L6" s="26"/>
@@ -3990,7 +3880,7 @@
       </c>
       <c r="D7" s="49">
         <f>SUMIFS(コスト表!D:D, コスト表!B:B, "敵3(遠距離型ゾンビ)", コスト表!G:G, "完了")</f>
-        <v>7.5</v>
+        <v>9.5</v>
       </c>
       <c r="E7" s="49">
         <f>SUMIFS(コスト表!D:D, コスト表!B:B, "敵3(遠距離型ゾンビ)", コスト表!G:G, "作業中")</f>
@@ -3998,11 +3888,11 @@
       </c>
       <c r="F7" s="49">
         <f>SUMIFS(コスト表!D:D, コスト表!B:B, "敵3(遠距離型ゾンビ)", コスト表!G:G, "未着手")</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G7" s="38">
         <f>ROUNDDOWN(COUNTIFS(コスト表!B:B, "敵3(遠距離型ゾンビ)", コスト表!G:G, "完了") / COUNTIF(コスト表!B:B, "敵3(遠距離型ゾンビ)") * 100,1)</f>
-        <v>66.599999999999994</v>
+        <v>83.3</v>
       </c>
       <c r="M7" s="26"/>
     </row>
@@ -4016,19 +3906,19 @@
       </c>
       <c r="D8" s="49">
         <f>SUMIFS(コスト表!D:D, コスト表!B:B, "ボス(ゾンビを召喚)", コスト表!G:G, "完了")</f>
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="E8" s="49">
         <f>SUMIFS(コスト表!D:D, コスト表!B:B, "ボス(ゾンビを召喚)", コスト表!G:G, "作業中")</f>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F8" s="49">
         <f>SUMIFS(コスト表!D:D,コスト表!B:B,"ボス(ゾンビを召喚)",コスト表!G:G,"未着手")</f>
-        <v>24</v>
+        <v>4</v>
       </c>
       <c r="G8" s="38">
         <f>ROUNDDOWN(COUNTIFS(コスト表!B:B, "ボス(ゾンビを召喚)", コスト表!G:G, "完了") / COUNTIF(コスト表!B:B, "ボス(ゾンビを召喚)") * 100,1)</f>
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="I8" s="40" t="s">
         <v>4</v>
@@ -4084,19 +3974,19 @@
       </c>
       <c r="D10" s="49">
         <f>SUMIFS(コスト表!D:D, コスト表!B:B, "ウェーブ管理", コスト表!G:G, "完了")</f>
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="E10" s="49">
         <f>SUMIFS(コスト表!D:D, コスト表!B:B, "ウェーブ管理", コスト表!G:G, "作業中")</f>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F10" s="49">
         <f>SUMIFS(コスト表!D:D, コスト表!B:B, "ウェーブ管理", コスト表!G:G, "未着手")</f>
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G10" s="38">
         <f>ROUNDDOWN(COUNTIFS(コスト表!B:B, "ウェーブ管理", コスト表!G:G, "完了") / COUNTIF(コスト表!B:B, "ウェーブ管理") * 100,1)</f>
-        <v>62.5</v>
+        <v>87.5</v>
       </c>
       <c r="I10" s="41" t="s">
         <v>126</v>
@@ -4164,7 +4054,7 @@
       </c>
       <c r="D12" s="49">
         <f>SUMIFS(コスト表!D:D, コスト表!B:B, "タイトル", コスト表!G:G, "完了")</f>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E12" s="49">
         <f>SUMIFS(コスト表!D:D, コスト表!B:B, "タイトル", コスト表!G:G, "作業中")</f>
@@ -4172,11 +4062,11 @@
       </c>
       <c r="F12" s="49">
         <f>SUMIFS(コスト表!D:D, コスト表!B:B, "タイトル", コスト表!G:G, "未着手")</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G12" s="38">
         <f>ROUNDDOWN(COUNTIFS(コスト表!B:B, "タイトル", コスト表!G:G, "完了") / COUNTIF(コスト表!B:B, "タイトル") * 100,1)</f>
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="I12" s="41" t="s">
         <v>128</v>
@@ -4204,7 +4094,7 @@
       </c>
       <c r="D13" s="49">
         <f>SUMIFS(コスト表!D:D, コスト表!B:B, "リザルト", コスト表!G:G, "完了")</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E13" s="49">
         <f>SUMIFS(コスト表!D:D, コスト表!B:B, "リザルト", コスト表!G:G, "作業中")</f>
@@ -4212,11 +4102,11 @@
       </c>
       <c r="F13" s="49">
         <f>SUMIFS(コスト表!D:D, コスト表!B:B, "リザルト", コスト表!G:G, "未着手")</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G13" s="38">
         <f>ROUNDDOWN(COUNTIFS(コスト表!B:B, "リザルト", コスト表!G:G, "完了") / COUNTIF(コスト表!B:B, "リザルト") * 100,1)</f>
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="J13" s="44"/>
       <c r="K13" s="42"/>
@@ -4257,7 +4147,7 @@
       </c>
       <c r="D15" s="56">
         <f>SUMIFS(コスト表!D:D, コスト表!B:B, "ゲームオーバー", コスト表!G:G, "完了")</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E15" s="56">
         <f>SUMIFS(コスト表!D:D, コスト表!B:B, "ゲームオーバー", コスト表!G:G, "作業中")</f>
@@ -4265,11 +4155,11 @@
       </c>
       <c r="F15" s="56">
         <f>SUMIFS(コスト表!D:D, コスト表!B:B, "ゲームオーバー", コスト表!G:G, "未着手")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G15" s="41">
         <f>ROUNDDOWN(COUNTIFS(コスト表!B:B, "ゲームオーバー", コスト表!G:G, "完了") / COUNTIF(コスト表!B:B, "ゲームオーバー") * 100,1)</f>
-        <v>75</v>
+        <v>100</v>
       </c>
     </row>
     <row r="16" spans="2:13">
@@ -4282,7 +4172,7 @@
       <c r="F16" s="9"/>
       <c r="G16" s="38">
         <f>ROUNDDOWN(COUNTIF(コスト表!G:G, "完了") / COUNTA(コスト表!G:G) * 100,1)</f>
-        <v>56.4</v>
+        <v>77.599999999999994</v>
       </c>
     </row>
     <row r="19" spans="3:7">
@@ -4420,6 +4310,21 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="ドキュメント" ma:contentTypeID="0x0101006836AD0B55474E4CAD520F1DEB8FB579" ma:contentTypeVersion="3" ma:contentTypeDescription="新しいドキュメントを作成します。" ma:contentTypeScope="" ma:versionID="078ba6c1f7b5b638bb57eb024ae572f7">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="187a6309-4c0c-49e3-bd2d-e8130eb88270" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="c5f182963113af090d1b42042cf04cb6" ns2:_="">
     <xsd:import namespace="187a6309-4c0c-49e3-bd2d-e8130eb88270"/>
@@ -4557,22 +4462,24 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BC0DB335-AD01-472D-90D0-5B4B126AC491}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E90E09EE-5F6D-4AB8-AE54-C74368FE6F4B}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5A1D85CE-B20E-4841-A55B-779E85453EF9}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -4588,21 +4495,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E90E09EE-5F6D-4AB8-AE54-C74368FE6F4B}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BC0DB335-AD01-472D-90D0-5B4B126AC491}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>